--- a/Ledoit_Wolf_Results_monthly.xlsx
+++ b/Ledoit_Wolf_Results_monthly.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L175"/>
+  <dimension ref="A1:L174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,7 +502,7 @@
         <v>41030</v>
       </c>
       <c r="B2" t="n">
-        <v>17.2797</v>
+        <v>17.27969</v>
       </c>
       <c r="C2" t="n">
         <v>23.01618</v>
@@ -526,7 +526,7 @@
         <v>1.96667</v>
       </c>
       <c r="J2" t="n">
-        <v>18.13143</v>
+        <v>18.13144</v>
       </c>
       <c r="K2" t="n">
         <v>2.36238</v>
@@ -540,13 +540,13 @@
         <v>41061</v>
       </c>
       <c r="B3" t="n">
-        <v>17.46722</v>
+        <v>17.46723</v>
       </c>
       <c r="C3" t="n">
         <v>24.12007</v>
       </c>
       <c r="D3" t="n">
-        <v>14.37943</v>
+        <v>14.37944</v>
       </c>
       <c r="E3" t="n">
         <v>11.4175</v>
@@ -660,7 +660,7 @@
         <v>23.62107</v>
       </c>
       <c r="D6" t="n">
-        <v>18.70341</v>
+        <v>18.7034</v>
       </c>
       <c r="E6" t="n">
         <v>12.716</v>
@@ -678,7 +678,7 @@
         <v>1.952</v>
       </c>
       <c r="J6" t="n">
-        <v>16.03937</v>
+        <v>16.03938</v>
       </c>
       <c r="K6" t="n">
         <v>2.51111</v>
@@ -692,7 +692,7 @@
         <v>41183</v>
       </c>
       <c r="B7" t="n">
-        <v>17.88224</v>
+        <v>17.88225</v>
       </c>
       <c r="C7" t="n">
         <v>22.65273</v>
@@ -730,10 +730,10 @@
         <v>41214</v>
       </c>
       <c r="B8" t="n">
-        <v>17.66096</v>
+        <v>17.66097</v>
       </c>
       <c r="C8" t="n">
-        <v>21.30241</v>
+        <v>21.30242</v>
       </c>
       <c r="D8" t="n">
         <v>17.31199</v>
@@ -771,10 +771,10 @@
         <v>16.05836</v>
       </c>
       <c r="C9" t="n">
-        <v>21.37444</v>
+        <v>21.37443</v>
       </c>
       <c r="D9" t="n">
-        <v>17.53535</v>
+        <v>17.53534</v>
       </c>
       <c r="E9" t="n">
         <v>12.5435</v>
@@ -809,7 +809,7 @@
         <v>13.74452</v>
       </c>
       <c r="C10" t="n">
-        <v>21.96661</v>
+        <v>21.96662</v>
       </c>
       <c r="D10" t="n">
         <v>18.73291</v>
@@ -830,7 +830,7 @@
         <v>2.50067</v>
       </c>
       <c r="J10" t="n">
-        <v>15.04615</v>
+        <v>15.04616</v>
       </c>
       <c r="K10" t="n">
         <v>2.58865</v>
@@ -859,7 +859,7 @@
         <v>0.29316</v>
       </c>
       <c r="G11" t="n">
-        <v>26.99148</v>
+        <v>26.99149</v>
       </c>
       <c r="H11" t="n">
         <v>2.49</v>
@@ -888,7 +888,7 @@
         <v>23.08445</v>
       </c>
       <c r="D12" t="n">
-        <v>19.68728</v>
+        <v>19.68729</v>
       </c>
       <c r="E12" t="n">
         <v>13.3245</v>
@@ -897,7 +897,7 @@
         <v>0.29709</v>
       </c>
       <c r="G12" t="n">
-        <v>25.33732</v>
+        <v>25.33733</v>
       </c>
       <c r="H12" t="n">
         <v>2.55</v>
@@ -920,7 +920,7 @@
         <v>41365</v>
       </c>
       <c r="B13" t="n">
-        <v>13.43886</v>
+        <v>13.43887</v>
       </c>
       <c r="C13" t="n">
         <v>26.70728</v>
@@ -944,7 +944,7 @@
         <v>3.59933</v>
       </c>
       <c r="J13" t="n">
-        <v>17.31124</v>
+        <v>17.31123</v>
       </c>
       <c r="K13" t="n">
         <v>2.32522</v>
@@ -964,7 +964,7 @@
         <v>28.3571</v>
       </c>
       <c r="D14" t="n">
-        <v>21.5968</v>
+        <v>21.59679</v>
       </c>
       <c r="E14" t="n">
         <v>13.46</v>
@@ -982,7 +982,7 @@
         <v>6.51733</v>
       </c>
       <c r="J14" t="n">
-        <v>17.71509</v>
+        <v>17.71508</v>
       </c>
       <c r="K14" t="n">
         <v>2.74501</v>
@@ -1037,10 +1037,10 @@
         <v>13.8257</v>
       </c>
       <c r="C16" t="n">
-        <v>25.87077</v>
+        <v>25.87078</v>
       </c>
       <c r="D16" t="n">
-        <v>22.00655</v>
+        <v>22.00656</v>
       </c>
       <c r="E16" t="n">
         <v>15.061</v>
@@ -1113,7 +1113,7 @@
         <v>14.66184</v>
       </c>
       <c r="C18" t="n">
-        <v>27.23135</v>
+        <v>27.23136</v>
       </c>
       <c r="D18" t="n">
         <v>21.71305</v>
@@ -1125,7 +1125,7 @@
         <v>0.36396</v>
       </c>
       <c r="G18" t="n">
-        <v>49.75347</v>
+        <v>49.75348</v>
       </c>
       <c r="H18" t="n">
         <v>3.81</v>
@@ -1148,10 +1148,10 @@
         <v>41548</v>
       </c>
       <c r="B19" t="n">
-        <v>16.07497</v>
+        <v>16.07498</v>
       </c>
       <c r="C19" t="n">
-        <v>28.97422</v>
+        <v>28.97423</v>
       </c>
       <c r="D19" t="n">
         <v>25.54719</v>
@@ -1163,7 +1163,7 @@
         <v>0.35531</v>
       </c>
       <c r="G19" t="n">
-        <v>49.73367</v>
+        <v>49.73366</v>
       </c>
       <c r="H19" t="n">
         <v>3.34</v>
@@ -1172,7 +1172,7 @@
         <v>10.66267</v>
       </c>
       <c r="J19" t="n">
-        <v>18.02841</v>
+        <v>18.0284</v>
       </c>
       <c r="K19" t="n">
         <v>3.3442</v>
@@ -1189,7 +1189,7 @@
         <v>17.20107</v>
       </c>
       <c r="C20" t="n">
-        <v>31.4365</v>
+        <v>31.43649</v>
       </c>
       <c r="D20" t="n">
         <v>26.26632</v>
@@ -1224,10 +1224,10 @@
         <v>41609</v>
       </c>
       <c r="B21" t="n">
-        <v>17.3542</v>
+        <v>17.35419</v>
       </c>
       <c r="C21" t="n">
-        <v>30.84288</v>
+        <v>30.84289</v>
       </c>
       <c r="D21" t="n">
         <v>27.78144</v>
@@ -1248,7 +1248,7 @@
         <v>10.02867</v>
       </c>
       <c r="J21" t="n">
-        <v>19.30522</v>
+        <v>19.30521</v>
       </c>
       <c r="K21" t="n">
         <v>3.91087</v>
@@ -1262,10 +1262,10 @@
         <v>41640</v>
       </c>
       <c r="B22" t="n">
-        <v>15.48521</v>
+        <v>15.4852</v>
       </c>
       <c r="C22" t="n">
-        <v>31.19739</v>
+        <v>31.1974</v>
       </c>
       <c r="D22" t="n">
         <v>29.27523</v>
@@ -1286,7 +1286,7 @@
         <v>12.094</v>
       </c>
       <c r="J22" t="n">
-        <v>18.24923</v>
+        <v>18.24922</v>
       </c>
       <c r="K22" t="n">
         <v>4.04103</v>
@@ -1324,7 +1324,7 @@
         <v>16.32067</v>
       </c>
       <c r="J23" t="n">
-        <v>18.58842</v>
+        <v>18.58841</v>
       </c>
       <c r="K23" t="n">
         <v>4.56317</v>
@@ -1341,7 +1341,7 @@
         <v>16.70252</v>
       </c>
       <c r="C24" t="n">
-        <v>34.04784</v>
+        <v>34.04785</v>
       </c>
       <c r="D24" t="n">
         <v>27.62774</v>
@@ -1353,7 +1353,7 @@
         <v>0.4231</v>
       </c>
       <c r="G24" t="n">
-        <v>59.66852</v>
+        <v>59.66851</v>
       </c>
       <c r="H24" t="n">
         <v>4.01</v>
@@ -1376,10 +1376,10 @@
         <v>41730</v>
       </c>
       <c r="B25" t="n">
-        <v>18.36269</v>
+        <v>18.36268</v>
       </c>
       <c r="C25" t="n">
-        <v>33.55777</v>
+        <v>33.55775</v>
       </c>
       <c r="D25" t="n">
         <v>26.49191</v>
@@ -1417,7 +1417,7 @@
         <v>19.808</v>
       </c>
       <c r="C26" t="n">
-        <v>34.24621</v>
+        <v>34.24623</v>
       </c>
       <c r="D26" t="n">
         <v>28.31308</v>
@@ -1438,7 +1438,7 @@
         <v>13.85133</v>
       </c>
       <c r="J26" t="n">
-        <v>20.68656</v>
+        <v>20.68655</v>
       </c>
       <c r="K26" t="n">
         <v>5.24892</v>
@@ -1452,13 +1452,13 @@
         <v>41791</v>
       </c>
       <c r="B27" t="n">
-        <v>20.35593</v>
+        <v>20.35592</v>
       </c>
       <c r="C27" t="n">
-        <v>34.88196</v>
+        <v>34.88197</v>
       </c>
       <c r="D27" t="n">
-        <v>28.95794</v>
+        <v>28.95795</v>
       </c>
       <c r="E27" t="n">
         <v>16.239</v>
@@ -1479,7 +1479,7 @@
         <v>23.39731</v>
       </c>
       <c r="K27" t="n">
-        <v>5.37489</v>
+        <v>5.3749</v>
       </c>
       <c r="L27" t="n">
         <v>1960.22998</v>
@@ -1505,7 +1505,7 @@
         <v>0.41532</v>
       </c>
       <c r="G28" t="n">
-        <v>71.96079</v>
+        <v>71.96078</v>
       </c>
       <c r="H28" t="n">
         <v>3.91</v>
@@ -1514,7 +1514,7 @@
         <v>14.88667</v>
       </c>
       <c r="J28" t="n">
-        <v>25.66133</v>
+        <v>25.66132</v>
       </c>
       <c r="K28" t="n">
         <v>5.17428</v>
@@ -1528,7 +1528,7 @@
         <v>41852</v>
       </c>
       <c r="B29" t="n">
-        <v>22.56387</v>
+        <v>22.56388</v>
       </c>
       <c r="C29" t="n">
         <v>38.23945</v>
@@ -1543,7 +1543,7 @@
         <v>0.46364</v>
       </c>
       <c r="G29" t="n">
-        <v>74.11020000000001</v>
+        <v>74.11019</v>
       </c>
       <c r="H29" t="n">
         <v>4.17</v>
@@ -1555,7 +1555,7 @@
         <v>26.61712</v>
       </c>
       <c r="K29" t="n">
-        <v>6.12217</v>
+        <v>6.12218</v>
       </c>
       <c r="L29" t="n">
         <v>2003.37</v>
@@ -1566,10 +1566,10 @@
         <v>41883</v>
       </c>
       <c r="B30" t="n">
-        <v>22.17863</v>
+        <v>22.17864</v>
       </c>
       <c r="C30" t="n">
-        <v>39.02225</v>
+        <v>39.02224</v>
       </c>
       <c r="D30" t="n">
         <v>29.14318</v>
@@ -1581,7 +1581,7 @@
         <v>0.43981</v>
       </c>
       <c r="G30" t="n">
-        <v>78.29018000000001</v>
+        <v>78.29017</v>
       </c>
       <c r="H30" t="n">
         <v>3.41</v>
@@ -1590,7 +1590,7 @@
         <v>16.17867</v>
       </c>
       <c r="J30" t="n">
-        <v>26.54091</v>
+        <v>26.54089</v>
       </c>
       <c r="K30" t="n">
         <v>6.51206</v>
@@ -1607,7 +1607,7 @@
         <v>23.77462</v>
       </c>
       <c r="C31" t="n">
-        <v>39.51886</v>
+        <v>39.51888</v>
       </c>
       <c r="D31" t="n">
         <v>28.12586</v>
@@ -1619,7 +1619,7 @@
         <v>0.46579</v>
       </c>
       <c r="G31" t="n">
-        <v>74.27858000000001</v>
+        <v>74.27857</v>
       </c>
       <c r="H31" t="n">
         <v>2.8</v>
@@ -1628,7 +1628,7 @@
         <v>16.11333</v>
       </c>
       <c r="J31" t="n">
-        <v>25.9235</v>
+        <v>25.92349</v>
       </c>
       <c r="K31" t="n">
         <v>6.45592</v>
@@ -1657,7 +1657,7 @@
         <v>0.50199</v>
       </c>
       <c r="G32" t="n">
-        <v>76.96288</v>
+        <v>76.96287</v>
       </c>
       <c r="H32" t="n">
         <v>2.79</v>
@@ -1695,7 +1695,7 @@
         <v>0.47997</v>
       </c>
       <c r="G33" t="n">
-        <v>77.27982</v>
+        <v>77.27983999999999</v>
       </c>
       <c r="H33" t="n">
         <v>2.67</v>
@@ -1724,7 +1724,7 @@
         <v>34.22007</v>
       </c>
       <c r="D34" t="n">
-        <v>26.62415</v>
+        <v>26.62416</v>
       </c>
       <c r="E34" t="n">
         <v>17.7265</v>
@@ -1756,10 +1756,10 @@
         <v>42036</v>
       </c>
       <c r="B35" t="n">
-        <v>28.51329</v>
+        <v>28.5133</v>
       </c>
       <c r="C35" t="n">
-        <v>37.40665</v>
+        <v>37.40664</v>
       </c>
       <c r="D35" t="n">
         <v>27.86633</v>
@@ -1771,7 +1771,7 @@
         <v>0.53012</v>
       </c>
       <c r="G35" t="n">
-        <v>78.22083000000001</v>
+        <v>78.22082</v>
       </c>
       <c r="H35" t="n">
         <v>3.11</v>
@@ -1794,10 +1794,10 @@
         <v>42064</v>
       </c>
       <c r="B36" t="n">
-        <v>27.61878</v>
+        <v>27.61879</v>
       </c>
       <c r="C36" t="n">
-        <v>34.6854</v>
+        <v>34.68539</v>
       </c>
       <c r="D36" t="n">
         <v>27.47357</v>
@@ -1818,7 +1818,7 @@
         <v>12.58467</v>
       </c>
       <c r="J36" t="n">
-        <v>24.16335</v>
+        <v>24.16334</v>
       </c>
       <c r="K36" t="n">
         <v>9.567069999999999</v>
@@ -1873,7 +1873,7 @@
         <v>29.03806</v>
       </c>
       <c r="C38" t="n">
-        <v>40.23413</v>
+        <v>40.23415</v>
       </c>
       <c r="D38" t="n">
         <v>27.00899</v>
@@ -1908,7 +1908,7 @@
         <v>42156</v>
       </c>
       <c r="B39" t="n">
-        <v>27.95704</v>
+        <v>27.95705</v>
       </c>
       <c r="C39" t="n">
         <v>37.90733</v>
@@ -1923,7 +1923,7 @@
         <v>0.4855</v>
       </c>
       <c r="G39" t="n">
-        <v>84.95632000000001</v>
+        <v>84.95631</v>
       </c>
       <c r="H39" t="n">
         <v>2.4</v>
@@ -1932,7 +1932,7 @@
         <v>17.884</v>
       </c>
       <c r="J39" t="n">
-        <v>23.67651</v>
+        <v>23.6765</v>
       </c>
       <c r="K39" t="n">
         <v>10.04366</v>
@@ -1946,10 +1946,10 @@
         <v>42186</v>
       </c>
       <c r="B40" t="n">
-        <v>27.03651</v>
+        <v>27.0365</v>
       </c>
       <c r="C40" t="n">
-        <v>40.09676</v>
+        <v>40.09677</v>
       </c>
       <c r="D40" t="n">
         <v>32.56512</v>
@@ -1973,7 +1973,7 @@
         <v>22.53237</v>
       </c>
       <c r="K40" t="n">
-        <v>9.455080000000001</v>
+        <v>9.455069999999999</v>
       </c>
       <c r="L40" t="n">
         <v>2103.84009</v>
@@ -1990,7 +1990,7 @@
         <v>37.61282</v>
       </c>
       <c r="D41" t="n">
-        <v>32.08568</v>
+        <v>32.08569</v>
       </c>
       <c r="E41" t="n">
         <v>25.6445</v>
@@ -2008,7 +2008,7 @@
         <v>16.604</v>
       </c>
       <c r="J41" t="n">
-        <v>22.39779</v>
+        <v>22.3978</v>
       </c>
       <c r="K41" t="n">
         <v>9.51779</v>
@@ -2022,10 +2022,10 @@
         <v>42248</v>
       </c>
       <c r="B42" t="n">
-        <v>24.696</v>
+        <v>24.69601</v>
       </c>
       <c r="C42" t="n">
-        <v>38.25238</v>
+        <v>38.25236</v>
       </c>
       <c r="D42" t="n">
         <v>31.61764</v>
@@ -2037,7 +2037,7 @@
         <v>0.5976</v>
       </c>
       <c r="G42" t="n">
-        <v>89.04713</v>
+        <v>89.04714</v>
       </c>
       <c r="H42" t="n">
         <v>1.72</v>
@@ -2060,10 +2060,10 @@
         <v>42278</v>
       </c>
       <c r="B43" t="n">
-        <v>26.75587</v>
+        <v>26.75588</v>
       </c>
       <c r="C43" t="n">
-        <v>45.49493</v>
+        <v>45.49492</v>
       </c>
       <c r="D43" t="n">
         <v>36.52197</v>
@@ -2125,7 +2125,7 @@
         <v>27.47923</v>
       </c>
       <c r="K44" t="n">
-        <v>9.88719</v>
+        <v>9.887180000000001</v>
       </c>
       <c r="L44" t="n">
         <v>2080.40991</v>
@@ -2136,7 +2136,7 @@
         <v>42339</v>
       </c>
       <c r="B45" t="n">
-        <v>23.66844</v>
+        <v>23.66843</v>
       </c>
       <c r="C45" t="n">
         <v>48.27262</v>
@@ -2151,7 +2151,7 @@
         <v>0.8021</v>
       </c>
       <c r="G45" t="n">
-        <v>103.66711</v>
+        <v>103.66712</v>
       </c>
       <c r="H45" t="n">
         <v>2.87</v>
@@ -2160,7 +2160,7 @@
         <v>16.00067</v>
       </c>
       <c r="J45" t="n">
-        <v>27.22633</v>
+        <v>27.22632</v>
       </c>
       <c r="K45" t="n">
         <v>11.03523</v>
@@ -2180,7 +2180,7 @@
         <v>47.93329</v>
       </c>
       <c r="D46" t="n">
-        <v>37.70868</v>
+        <v>37.70867</v>
       </c>
       <c r="E46" t="n">
         <v>29.35</v>
@@ -2198,10 +2198,10 @@
         <v>12.74667</v>
       </c>
       <c r="J46" t="n">
-        <v>24.51554</v>
+        <v>24.51555</v>
       </c>
       <c r="K46" t="n">
-        <v>10.16549</v>
+        <v>10.16548</v>
       </c>
       <c r="L46" t="n">
         <v>1940.23999</v>
@@ -2212,7 +2212,7 @@
         <v>42401</v>
       </c>
       <c r="B47" t="n">
-        <v>21.85939</v>
+        <v>21.85938</v>
       </c>
       <c r="C47" t="n">
         <v>44.58807</v>
@@ -2227,7 +2227,7 @@
         <v>0.76595</v>
       </c>
       <c r="G47" t="n">
-        <v>105.90566</v>
+        <v>105.90567</v>
       </c>
       <c r="H47" t="n">
         <v>2.14</v>
@@ -2239,7 +2239,7 @@
         <v>23.59122</v>
       </c>
       <c r="K47" t="n">
-        <v>10.18526</v>
+        <v>10.18525</v>
       </c>
       <c r="L47" t="n">
         <v>1932.22998</v>
@@ -2250,7 +2250,7 @@
         <v>42430</v>
       </c>
       <c r="B48" t="n">
-        <v>24.64014</v>
+        <v>24.64013</v>
       </c>
       <c r="C48" t="n">
         <v>48.40014</v>
@@ -2300,10 +2300,10 @@
         <v>32.9795</v>
       </c>
       <c r="F49" t="n">
-        <v>0.86779</v>
+        <v>0.8678</v>
       </c>
       <c r="G49" t="n">
-        <v>116.46454</v>
+        <v>116.46453</v>
       </c>
       <c r="H49" t="n">
         <v>3.55</v>
@@ -2326,10 +2326,10 @@
         <v>42491</v>
       </c>
       <c r="B50" t="n">
-        <v>22.71351</v>
+        <v>22.7135</v>
       </c>
       <c r="C50" t="n">
-        <v>46.77075</v>
+        <v>46.77076</v>
       </c>
       <c r="D50" t="n">
         <v>37.08957</v>
@@ -2341,7 +2341,7 @@
         <v>1.14407</v>
       </c>
       <c r="G50" t="n">
-        <v>117.68286</v>
+        <v>117.68287</v>
       </c>
       <c r="H50" t="n">
         <v>4.57</v>
@@ -2350,7 +2350,7 @@
         <v>14.882</v>
       </c>
       <c r="J50" t="n">
-        <v>25.40332</v>
+        <v>25.40333</v>
       </c>
       <c r="K50" t="n">
         <v>11.77429</v>
@@ -2367,7 +2367,7 @@
         <v>21.74455</v>
       </c>
       <c r="C51" t="n">
-        <v>45.15585</v>
+        <v>45.15584</v>
       </c>
       <c r="D51" t="n">
         <v>34.84492</v>
@@ -2388,10 +2388,10 @@
         <v>14.152</v>
       </c>
       <c r="J51" t="n">
-        <v>26.37635</v>
+        <v>26.37634</v>
       </c>
       <c r="K51" t="n">
-        <v>11.89101</v>
+        <v>11.89102</v>
       </c>
       <c r="L51" t="n">
         <v>2098.86011</v>
@@ -2405,7 +2405,7 @@
         <v>23.70293</v>
       </c>
       <c r="C52" t="n">
-        <v>50.01823</v>
+        <v>50.01824</v>
       </c>
       <c r="D52" t="n">
         <v>39.19404</v>
@@ -2417,7 +2417,7 @@
         <v>1.39825</v>
       </c>
       <c r="G52" t="n">
-        <v>122.76419</v>
+        <v>122.76421</v>
       </c>
       <c r="H52" t="n">
         <v>6.86</v>
@@ -2440,13 +2440,13 @@
         <v>42583</v>
       </c>
       <c r="B53" t="n">
-        <v>24.26355</v>
+        <v>24.26354</v>
       </c>
       <c r="C53" t="n">
         <v>51.02259</v>
       </c>
       <c r="D53" t="n">
-        <v>39.12024</v>
+        <v>39.12025</v>
       </c>
       <c r="E53" t="n">
         <v>38.458</v>
@@ -2455,7 +2455,7 @@
         <v>1.50484</v>
       </c>
       <c r="G53" t="n">
-        <v>124.92352</v>
+        <v>124.92353</v>
       </c>
       <c r="H53" t="n">
         <v>7.4</v>
@@ -2464,7 +2464,7 @@
         <v>14.134</v>
       </c>
       <c r="J53" t="n">
-        <v>29.07996</v>
+        <v>29.07997</v>
       </c>
       <c r="K53" t="n">
         <v>13.49944</v>
@@ -2531,7 +2531,7 @@
         <v>1.74576</v>
       </c>
       <c r="G55" t="n">
-        <v>129.74731</v>
+        <v>129.74733</v>
       </c>
       <c r="H55" t="n">
         <v>7.23</v>
@@ -2557,10 +2557,10 @@
         <v>25.4041</v>
       </c>
       <c r="C56" t="n">
-        <v>53.87038</v>
+        <v>53.87039</v>
       </c>
       <c r="D56" t="n">
-        <v>38.42832</v>
+        <v>38.42833</v>
       </c>
       <c r="E56" t="n">
         <v>37.5285</v>
@@ -2592,7 +2592,7 @@
         <v>42705</v>
       </c>
       <c r="B57" t="n">
-        <v>26.62235</v>
+        <v>26.62236</v>
       </c>
       <c r="C57" t="n">
         <v>55.55105</v>
@@ -2607,7 +2607,7 @@
         <v>2.62256</v>
       </c>
       <c r="G57" t="n">
-        <v>113.95856</v>
+        <v>113.95855</v>
       </c>
       <c r="H57" t="n">
         <v>11.34</v>
@@ -2616,7 +2616,7 @@
         <v>14.246</v>
       </c>
       <c r="J57" t="n">
-        <v>29.61037</v>
+        <v>29.61036</v>
       </c>
       <c r="K57" t="n">
         <v>13.64458</v>
@@ -2654,7 +2654,7 @@
         <v>16.79533</v>
       </c>
       <c r="J58" t="n">
-        <v>30.05938</v>
+        <v>30.05939</v>
       </c>
       <c r="K58" t="n">
         <v>15.39907</v>
@@ -2668,7 +2668,7 @@
         <v>42767</v>
       </c>
       <c r="B59" t="n">
-        <v>31.62501</v>
+        <v>31.62502</v>
       </c>
       <c r="C59" t="n">
         <v>57.5427</v>
@@ -2692,7 +2692,7 @@
         <v>16.666</v>
       </c>
       <c r="J59" t="n">
-        <v>29.76419</v>
+        <v>29.7642</v>
       </c>
       <c r="K59" t="n">
         <v>16.28133</v>
@@ -2706,7 +2706,7 @@
         <v>42795</v>
       </c>
       <c r="B60" t="n">
-        <v>33.16482</v>
+        <v>33.16483</v>
       </c>
       <c r="C60" t="n">
         <v>59.23354</v>
@@ -2721,7 +2721,7 @@
         <v>2.67974</v>
       </c>
       <c r="G60" t="n">
-        <v>140.70238</v>
+        <v>140.70241</v>
       </c>
       <c r="H60" t="n">
         <v>14.55</v>
@@ -2730,10 +2730,10 @@
         <v>18.55333</v>
       </c>
       <c r="J60" t="n">
-        <v>29.65731</v>
+        <v>29.6573</v>
       </c>
       <c r="K60" t="n">
-        <v>16.9778</v>
+        <v>16.97781</v>
       </c>
       <c r="L60" t="n">
         <v>2362.71997</v>
@@ -2747,10 +2747,10 @@
         <v>33.16251</v>
       </c>
       <c r="C61" t="n">
-        <v>61.57195</v>
+        <v>61.57193</v>
       </c>
       <c r="D61" t="n">
-        <v>45.79028</v>
+        <v>45.79027</v>
       </c>
       <c r="E61" t="n">
         <v>46.2495</v>
@@ -2759,7 +2759,7 @@
         <v>2.56584</v>
       </c>
       <c r="G61" t="n">
-        <v>148.82462</v>
+        <v>148.82457</v>
       </c>
       <c r="H61" t="n">
         <v>13.3</v>
@@ -2768,10 +2768,10 @@
         <v>20.938</v>
       </c>
       <c r="J61" t="n">
-        <v>29.7231</v>
+        <v>29.72308</v>
       </c>
       <c r="K61" t="n">
-        <v>17.12125</v>
+        <v>17.12124</v>
       </c>
       <c r="L61" t="n">
         <v>2384.19995</v>
@@ -2782,10 +2782,10 @@
         <v>42856</v>
       </c>
       <c r="B62" t="n">
-        <v>35.41117</v>
+        <v>35.41118</v>
       </c>
       <c r="C62" t="n">
-        <v>63.17313</v>
+        <v>63.17314</v>
       </c>
       <c r="D62" t="n">
         <v>48.88928</v>
@@ -2797,7 +2797,7 @@
         <v>3.55483</v>
       </c>
       <c r="G62" t="n">
-        <v>150.02313</v>
+        <v>150.02315</v>
       </c>
       <c r="H62" t="n">
         <v>11.19</v>
@@ -2806,7 +2806,7 @@
         <v>22.734</v>
       </c>
       <c r="J62" t="n">
-        <v>29.91107</v>
+        <v>29.91108</v>
       </c>
       <c r="K62" t="n">
         <v>18.56889</v>
@@ -2820,7 +2820,7 @@
         <v>42887</v>
       </c>
       <c r="B63" t="n">
-        <v>33.38515</v>
+        <v>33.38517</v>
       </c>
       <c r="C63" t="n">
         <v>62.35</v>
@@ -2844,10 +2844,10 @@
         <v>24.10733</v>
       </c>
       <c r="J63" t="n">
-        <v>27.94793</v>
+        <v>27.94792</v>
       </c>
       <c r="K63" t="n">
-        <v>18.14728</v>
+        <v>18.14727</v>
       </c>
       <c r="L63" t="n">
         <v>2423.40991</v>
@@ -2858,13 +2858,13 @@
         <v>42917</v>
       </c>
       <c r="B64" t="n">
-        <v>34.47699</v>
+        <v>34.47697</v>
       </c>
       <c r="C64" t="n">
         <v>65.76012</v>
       </c>
       <c r="D64" t="n">
-        <v>46.82938</v>
+        <v>46.82939</v>
       </c>
       <c r="E64" t="n">
         <v>49.389</v>
@@ -2873,7 +2873,7 @@
         <v>4.00205</v>
       </c>
       <c r="G64" t="n">
-        <v>167.64438</v>
+        <v>167.64433</v>
       </c>
       <c r="H64" t="n">
         <v>13.61</v>
@@ -2896,10 +2896,10 @@
         <v>42948</v>
       </c>
       <c r="B65" t="n">
-        <v>38.16601</v>
+        <v>38.166</v>
       </c>
       <c r="C65" t="n">
-        <v>67.99285999999999</v>
+        <v>67.99284</v>
       </c>
       <c r="D65" t="n">
         <v>47.3118</v>
@@ -2908,10 +2908,10 @@
         <v>49.03</v>
       </c>
       <c r="F65" t="n">
-        <v>4.17639</v>
+        <v>4.17638</v>
       </c>
       <c r="G65" t="n">
-        <v>170.33853</v>
+        <v>170.33855</v>
       </c>
       <c r="H65" t="n">
         <v>13</v>
@@ -2920,7 +2920,7 @@
         <v>23.72667</v>
       </c>
       <c r="J65" t="n">
-        <v>29.26768</v>
+        <v>29.26767</v>
       </c>
       <c r="K65" t="n">
         <v>19.62833</v>
@@ -2934,13 +2934,13 @@
         <v>42979</v>
       </c>
       <c r="B66" t="n">
-        <v>35.86673</v>
+        <v>35.86674</v>
       </c>
       <c r="C66" t="n">
-        <v>67.73823</v>
+        <v>67.73824</v>
       </c>
       <c r="D66" t="n">
-        <v>48.22709</v>
+        <v>48.22708</v>
       </c>
       <c r="E66" t="n">
         <v>48.0675</v>
@@ -2949,7 +2949,7 @@
         <v>4.40636</v>
       </c>
       <c r="G66" t="n">
-        <v>169.24898</v>
+        <v>169.24901</v>
       </c>
       <c r="H66" t="n">
         <v>12.75</v>
@@ -2972,10 +2972,10 @@
         <v>43009</v>
       </c>
       <c r="B67" t="n">
-        <v>39.33891</v>
+        <v>39.33892</v>
       </c>
       <c r="C67" t="n">
-        <v>75.64058</v>
+        <v>75.64060000000001</v>
       </c>
       <c r="D67" t="n">
         <v>51.16513</v>
@@ -2987,7 +2987,7 @@
         <v>5.09749</v>
       </c>
       <c r="G67" t="n">
-        <v>178.35181</v>
+        <v>178.35179</v>
       </c>
       <c r="H67" t="n">
         <v>10.99</v>
@@ -2996,7 +2996,7 @@
         <v>22.102</v>
       </c>
       <c r="J67" t="n">
-        <v>37.96369</v>
+        <v>37.9637</v>
       </c>
       <c r="K67" t="n">
         <v>20.6343</v>
@@ -3010,10 +3010,10 @@
         <v>43040</v>
       </c>
       <c r="B68" t="n">
-        <v>40.13662</v>
+        <v>40.13663</v>
       </c>
       <c r="C68" t="n">
-        <v>76.92525000000001</v>
+        <v>76.92522</v>
       </c>
       <c r="D68" t="n">
         <v>51.32015</v>
@@ -3025,7 +3025,7 @@
         <v>4.95057</v>
       </c>
       <c r="G68" t="n">
-        <v>175.49913</v>
+        <v>175.49911</v>
       </c>
       <c r="H68" t="n">
         <v>10.89</v>
@@ -3034,7 +3034,7 @@
         <v>20.59</v>
       </c>
       <c r="J68" t="n">
-        <v>37.643</v>
+        <v>37.64299</v>
       </c>
       <c r="K68" t="n">
         <v>21.73126</v>
@@ -3048,10 +3048,10 @@
         <v>43070</v>
       </c>
       <c r="B69" t="n">
-        <v>39.52471</v>
+        <v>39.5247</v>
       </c>
       <c r="C69" t="n">
-        <v>78.17731999999999</v>
+        <v>78.17731000000001</v>
       </c>
       <c r="D69" t="n">
         <v>52.17353</v>
@@ -3060,7 +3060,7 @@
         <v>58.4735</v>
       </c>
       <c r="F69" t="n">
-        <v>4.77274</v>
+        <v>4.77273</v>
       </c>
       <c r="G69" t="n">
         <v>174.78596</v>
@@ -3072,7 +3072,7 @@
         <v>20.75667</v>
       </c>
       <c r="J69" t="n">
-        <v>38.75114</v>
+        <v>38.75113</v>
       </c>
       <c r="K69" t="n">
         <v>20.21936</v>
@@ -3086,13 +3086,13 @@
         <v>43101</v>
       </c>
       <c r="B70" t="n">
-        <v>39.10429</v>
+        <v>39.10431</v>
       </c>
       <c r="C70" t="n">
-        <v>86.83221</v>
+        <v>86.83222000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>58.55383</v>
+        <v>58.55382</v>
       </c>
       <c r="E70" t="n">
         <v>72.5445</v>
@@ -3101,7 +3101,7 @@
         <v>6.06273</v>
       </c>
       <c r="G70" t="n">
-        <v>185.117</v>
+        <v>185.11699</v>
       </c>
       <c r="H70" t="n">
         <v>13.74</v>
@@ -3127,7 +3127,7 @@
         <v>41.77063</v>
       </c>
       <c r="C71" t="n">
-        <v>86.10151</v>
+        <v>86.10149</v>
       </c>
       <c r="D71" t="n">
         <v>54.67573</v>
@@ -3139,7 +3139,7 @@
         <v>5.97271</v>
       </c>
       <c r="G71" t="n">
-        <v>176.62831</v>
+        <v>176.6283</v>
       </c>
       <c r="H71" t="n">
         <v>12.11</v>
@@ -3165,10 +3165,10 @@
         <v>39.34582</v>
       </c>
       <c r="C72" t="n">
-        <v>83.80595</v>
+        <v>83.80597</v>
       </c>
       <c r="D72" t="n">
-        <v>51.36819</v>
+        <v>51.3682</v>
       </c>
       <c r="E72" t="n">
         <v>72.367</v>
@@ -3177,7 +3177,7 @@
         <v>5.71579</v>
       </c>
       <c r="G72" t="n">
-        <v>158.27409</v>
+        <v>158.27411</v>
       </c>
       <c r="H72" t="n">
         <v>10.05</v>
@@ -3186,10 +3186,10 @@
         <v>17.742</v>
       </c>
       <c r="J72" t="n">
-        <v>44.01757</v>
+        <v>44.01756</v>
       </c>
       <c r="K72" t="n">
-        <v>18.81865</v>
+        <v>18.81864</v>
       </c>
       <c r="L72" t="n">
         <v>2640.87012</v>
@@ -3200,13 +3200,13 @@
         <v>43191</v>
       </c>
       <c r="B73" t="n">
-        <v>38.75486</v>
+        <v>38.75485</v>
       </c>
       <c r="C73" t="n">
-        <v>85.87196</v>
+        <v>85.87197</v>
       </c>
       <c r="D73" t="n">
-        <v>50.44894</v>
+        <v>50.44895</v>
       </c>
       <c r="E73" t="n">
         <v>78.3065</v>
@@ -3215,7 +3215,7 @@
         <v>5.55067</v>
       </c>
       <c r="G73" t="n">
-        <v>170.36827</v>
+        <v>170.36826</v>
       </c>
       <c r="H73" t="n">
         <v>10.88</v>
@@ -3241,10 +3241,10 @@
         <v>43.99157</v>
       </c>
       <c r="C74" t="n">
-        <v>91.15027000000001</v>
+        <v>91.15025</v>
       </c>
       <c r="D74" t="n">
-        <v>54.48157</v>
+        <v>54.48156</v>
       </c>
       <c r="E74" t="n">
         <v>81.48099999999999</v>
@@ -3262,7 +3262,7 @@
         <v>18.982</v>
       </c>
       <c r="J74" t="n">
-        <v>46.92382</v>
+        <v>46.92383</v>
       </c>
       <c r="K74" t="n">
         <v>20.12992</v>
@@ -3276,10 +3276,10 @@
         <v>43252</v>
       </c>
       <c r="B75" t="n">
-        <v>43.57723</v>
+        <v>43.57724</v>
       </c>
       <c r="C75" t="n">
-        <v>90.93814</v>
+        <v>90.93816</v>
       </c>
       <c r="D75" t="n">
         <v>55.92731</v>
@@ -3291,7 +3291,7 @@
         <v>5.85046</v>
       </c>
       <c r="G75" t="n">
-        <v>192.47653</v>
+        <v>192.47652</v>
       </c>
       <c r="H75" t="n">
         <v>14.99</v>
@@ -3314,13 +3314,13 @@
         <v>43282</v>
       </c>
       <c r="B76" t="n">
-        <v>44.79667</v>
+        <v>44.79666</v>
       </c>
       <c r="C76" t="n">
-        <v>97.82699</v>
+        <v>97.82697</v>
       </c>
       <c r="D76" t="n">
-        <v>60.78261</v>
+        <v>60.78262</v>
       </c>
       <c r="E76" t="n">
         <v>88.872</v>
@@ -3338,7 +3338,7 @@
         <v>19.876</v>
       </c>
       <c r="J76" t="n">
-        <v>40.88832</v>
+        <v>40.88833</v>
       </c>
       <c r="K76" t="n">
         <v>17.9477</v>
@@ -3355,10 +3355,10 @@
         <v>53.77492</v>
       </c>
       <c r="C77" t="n">
-        <v>103.9894</v>
+        <v>103.98939</v>
       </c>
       <c r="D77" t="n">
-        <v>61.00946</v>
+        <v>61.00945</v>
       </c>
       <c r="E77" t="n">
         <v>100.6355</v>
@@ -3367,7 +3367,7 @@
         <v>6.93543</v>
       </c>
       <c r="G77" t="n">
-        <v>174.06285</v>
+        <v>174.06288</v>
       </c>
       <c r="H77" t="n">
         <v>25.17</v>
@@ -3376,7 +3376,7 @@
         <v>20.11067</v>
       </c>
       <c r="J77" t="n">
-        <v>41.41923</v>
+        <v>41.41922</v>
       </c>
       <c r="K77" t="n">
         <v>17.72595</v>
@@ -3393,19 +3393,19 @@
         <v>53.32843</v>
       </c>
       <c r="C78" t="n">
-        <v>105.87792</v>
+        <v>105.87793</v>
       </c>
       <c r="D78" t="n">
-        <v>59.78511</v>
+        <v>59.7851</v>
       </c>
       <c r="E78" t="n">
         <v>100.15</v>
       </c>
       <c r="F78" t="n">
-        <v>6.94383</v>
+        <v>6.94384</v>
       </c>
       <c r="G78" t="n">
-        <v>162.89978</v>
+        <v>162.8998</v>
       </c>
       <c r="H78" t="n">
         <v>30.89</v>
@@ -3428,10 +3428,10 @@
         <v>43374</v>
       </c>
       <c r="B79" t="n">
-        <v>51.70311</v>
+        <v>51.70312</v>
       </c>
       <c r="C79" t="n">
-        <v>98.87926</v>
+        <v>98.87924</v>
       </c>
       <c r="D79" t="n">
         <v>54.01501</v>
@@ -3443,7 +3443,7 @@
         <v>5.20948</v>
       </c>
       <c r="G79" t="n">
-        <v>150.34996</v>
+        <v>150.35001</v>
       </c>
       <c r="H79" t="n">
         <v>18.21</v>
@@ -3481,7 +3481,7 @@
         <v>4.0423</v>
       </c>
       <c r="G80" t="n">
-        <v>139.27605</v>
+        <v>139.27606</v>
       </c>
       <c r="H80" t="n">
         <v>21.3</v>
@@ -3493,7 +3493,7 @@
         <v>42.43723</v>
       </c>
       <c r="K80" t="n">
-        <v>19.3577</v>
+        <v>19.35769</v>
       </c>
       <c r="L80" t="n">
         <v>2760.16992</v>
@@ -3504,13 +3504,13 @@
         <v>43435</v>
       </c>
       <c r="B81" t="n">
-        <v>37.39424</v>
+        <v>37.39425</v>
       </c>
       <c r="C81" t="n">
-        <v>94.43454</v>
+        <v>94.43452000000001</v>
       </c>
       <c r="D81" t="n">
-        <v>51.75552</v>
+        <v>51.75551</v>
       </c>
       <c r="E81" t="n">
         <v>75.0985</v>
@@ -3519,7 +3519,7 @@
         <v>3.30201</v>
       </c>
       <c r="G81" t="n">
-        <v>129.84639</v>
+        <v>129.84636</v>
       </c>
       <c r="H81" t="n">
         <v>18.46</v>
@@ -3528,7 +3528,7 @@
         <v>22.18667</v>
       </c>
       <c r="J81" t="n">
-        <v>40.38896</v>
+        <v>40.38894</v>
       </c>
       <c r="K81" t="n">
         <v>20.9517</v>
@@ -3545,10 +3545,10 @@
         <v>39.4567</v>
       </c>
       <c r="C82" t="n">
-        <v>97.0936</v>
+        <v>97.09362</v>
       </c>
       <c r="D82" t="n">
-        <v>55.76386</v>
+        <v>55.76387</v>
       </c>
       <c r="E82" t="n">
         <v>85.9365</v>
@@ -3557,7 +3557,7 @@
         <v>3.55553</v>
       </c>
       <c r="G82" t="n">
-        <v>165.10864</v>
+        <v>165.10866</v>
       </c>
       <c r="H82" t="n">
         <v>24.41</v>
@@ -3566,7 +3566,7 @@
         <v>20.468</v>
       </c>
       <c r="J82" t="n">
-        <v>40.55246</v>
+        <v>40.55247</v>
       </c>
       <c r="K82" t="n">
         <v>22.10278</v>
@@ -3580,10 +3580,10 @@
         <v>43497</v>
       </c>
       <c r="B83" t="n">
-        <v>41.22342</v>
+        <v>41.22344</v>
       </c>
       <c r="C83" t="n">
-        <v>104.60455</v>
+        <v>104.60454</v>
       </c>
       <c r="D83" t="n">
         <v>55.79656</v>
@@ -3595,7 +3595,7 @@
         <v>3.81942</v>
       </c>
       <c r="G83" t="n">
-        <v>159.91835</v>
+        <v>159.91833</v>
       </c>
       <c r="H83" t="n">
         <v>23.53</v>
@@ -3604,7 +3604,7 @@
         <v>21.32533</v>
       </c>
       <c r="J83" t="n">
-        <v>45.8674</v>
+        <v>45.86741</v>
       </c>
       <c r="K83" t="n">
         <v>22.68861</v>
@@ -3621,7 +3621,7 @@
         <v>45.22315</v>
       </c>
       <c r="C84" t="n">
-        <v>110.12281</v>
+        <v>110.12282</v>
       </c>
       <c r="D84" t="n">
         <v>58.28984</v>
@@ -3633,7 +3633,7 @@
         <v>4.44584</v>
       </c>
       <c r="G84" t="n">
-        <v>165.10864</v>
+        <v>165.10866</v>
       </c>
       <c r="H84" t="n">
         <v>25.52</v>
@@ -3656,10 +3656,10 @@
         <v>43556</v>
       </c>
       <c r="B85" t="n">
-        <v>47.77537</v>
+        <v>47.77536</v>
       </c>
       <c r="C85" t="n">
-        <v>121.9437</v>
+        <v>121.94372</v>
       </c>
       <c r="D85" t="n">
         <v>59.38293</v>
@@ -3671,7 +3671,7 @@
         <v>4.48149</v>
       </c>
       <c r="G85" t="n">
-        <v>191.56525</v>
+        <v>191.56523</v>
       </c>
       <c r="H85" t="n">
         <v>27.63</v>
@@ -3680,7 +3680,7 @@
         <v>15.91267</v>
       </c>
       <c r="J85" t="n">
-        <v>44.20454</v>
+        <v>44.20453</v>
       </c>
       <c r="K85" t="n">
         <v>26.4693</v>
@@ -3694,19 +3694,19 @@
         <v>43586</v>
       </c>
       <c r="B86" t="n">
-        <v>41.84104</v>
+        <v>41.84105</v>
       </c>
       <c r="C86" t="n">
-        <v>115.90984</v>
+        <v>115.90982</v>
       </c>
       <c r="D86" t="n">
-        <v>54.8035</v>
+        <v>54.80351</v>
       </c>
       <c r="E86" t="n">
         <v>88.7535</v>
       </c>
       <c r="F86" t="n">
-        <v>3.35777</v>
+        <v>3.35776</v>
       </c>
       <c r="G86" t="n">
         <v>175.78638</v>
@@ -3735,10 +3735,10 @@
         <v>47.30211</v>
       </c>
       <c r="C87" t="n">
-        <v>125.54402</v>
+        <v>125.54401</v>
       </c>
       <c r="D87" t="n">
-        <v>53.62967</v>
+        <v>53.62968</v>
       </c>
       <c r="E87" t="n">
         <v>94.6815</v>
@@ -3756,7 +3756,7 @@
         <v>14.89733</v>
       </c>
       <c r="J87" t="n">
-        <v>41.71298</v>
+        <v>41.71299</v>
       </c>
       <c r="K87" t="n">
         <v>24.15987</v>
@@ -3773,7 +3773,7 @@
         <v>50.91572</v>
       </c>
       <c r="C88" t="n">
-        <v>127.70882</v>
+        <v>127.70885</v>
       </c>
       <c r="D88" t="n">
         <v>60.33586</v>
@@ -3797,7 +3797,7 @@
         <v>44.04828</v>
       </c>
       <c r="K88" t="n">
-        <v>24.33865</v>
+        <v>24.33864</v>
       </c>
       <c r="L88" t="n">
         <v>2980.37988</v>
@@ -3811,7 +3811,7 @@
         <v>50.0776</v>
       </c>
       <c r="C89" t="n">
-        <v>129.62917</v>
+        <v>129.62924</v>
       </c>
       <c r="D89" t="n">
         <v>58.9654</v>
@@ -3823,7 +3823,7 @@
         <v>4.15633</v>
       </c>
       <c r="G89" t="n">
-        <v>183.90858</v>
+        <v>183.90855</v>
       </c>
       <c r="H89" t="n">
         <v>31.45</v>
@@ -3832,7 +3832,7 @@
         <v>15.04067</v>
       </c>
       <c r="J89" t="n">
-        <v>41.59107</v>
+        <v>41.59106</v>
       </c>
       <c r="K89" t="n">
         <v>23.72176</v>
@@ -3846,13 +3846,13 @@
         <v>43709</v>
       </c>
       <c r="B90" t="n">
-        <v>53.73133</v>
+        <v>53.73132</v>
       </c>
       <c r="C90" t="n">
-        <v>130.72937</v>
+        <v>130.72934</v>
       </c>
       <c r="D90" t="n">
-        <v>60.48148</v>
+        <v>60.48147</v>
       </c>
       <c r="E90" t="n">
         <v>86.7955</v>
@@ -3861,7 +3861,7 @@
         <v>4.3191</v>
       </c>
       <c r="G90" t="n">
-        <v>176.39059</v>
+        <v>176.39058</v>
       </c>
       <c r="H90" t="n">
         <v>28.99</v>
@@ -3870,10 +3870,10 @@
         <v>16.058</v>
       </c>
       <c r="J90" t="n">
-        <v>45.20539</v>
+        <v>45.2054</v>
       </c>
       <c r="K90" t="n">
-        <v>23.38355</v>
+        <v>23.38356</v>
       </c>
       <c r="L90" t="n">
         <v>2976.73999</v>
@@ -3884,7 +3884,7 @@
         <v>43739</v>
       </c>
       <c r="B91" t="n">
-        <v>59.67856</v>
+        <v>59.67855</v>
       </c>
       <c r="C91" t="n">
         <v>134.81023</v>
@@ -3899,7 +3899,7 @@
         <v>4.98779</v>
       </c>
       <c r="G91" t="n">
-        <v>189.83186</v>
+        <v>189.83185</v>
       </c>
       <c r="H91" t="n">
         <v>33.93</v>
@@ -3911,7 +3911,7 @@
         <v>49.59172</v>
       </c>
       <c r="K91" t="n">
-        <v>24.80484</v>
+        <v>24.80485</v>
       </c>
       <c r="L91" t="n">
         <v>3037.56006</v>
@@ -3922,10 +3922,10 @@
         <v>43770</v>
       </c>
       <c r="B92" t="n">
-        <v>64.30685</v>
+        <v>64.30688000000001</v>
       </c>
       <c r="C92" t="n">
-        <v>142.82639</v>
+        <v>142.82642</v>
       </c>
       <c r="D92" t="n">
         <v>64.58987</v>
@@ -3937,7 +3937,7 @@
         <v>5.38181</v>
       </c>
       <c r="G92" t="n">
-        <v>199.72708</v>
+        <v>199.72707</v>
       </c>
       <c r="H92" t="n">
         <v>39.15</v>
@@ -3960,13 +3960,13 @@
         <v>43800</v>
       </c>
       <c r="B93" t="n">
-        <v>70.65937</v>
+        <v>70.65936000000001</v>
       </c>
       <c r="C93" t="n">
-        <v>148.78928</v>
+        <v>148.78926</v>
       </c>
       <c r="D93" t="n">
-        <v>66.33824</v>
+        <v>66.33825</v>
       </c>
       <c r="E93" t="n">
         <v>92.392</v>
@@ -3984,7 +3984,7 @@
         <v>27.88867</v>
       </c>
       <c r="J93" t="n">
-        <v>52.7932</v>
+        <v>52.79321</v>
       </c>
       <c r="K93" t="n">
         <v>27.03852</v>
@@ -3998,13 +3998,13 @@
         <v>43831</v>
       </c>
       <c r="B94" t="n">
-        <v>74.47563</v>
+        <v>74.47566999999999</v>
       </c>
       <c r="C94" t="n">
-        <v>160.61127</v>
+        <v>160.61125</v>
       </c>
       <c r="D94" t="n">
-        <v>70.96372</v>
+        <v>70.96373</v>
       </c>
       <c r="E94" t="n">
         <v>100.436</v>
@@ -4013,7 +4013,7 @@
         <v>5.87073</v>
       </c>
       <c r="G94" t="n">
-        <v>199.99452</v>
+        <v>199.99451</v>
       </c>
       <c r="H94" t="n">
         <v>47</v>
@@ -4036,10 +4036,10 @@
         <v>43862</v>
       </c>
       <c r="B95" t="n">
-        <v>65.9332</v>
+        <v>65.93321</v>
       </c>
       <c r="C95" t="n">
-        <v>153.27324</v>
+        <v>153.27321</v>
       </c>
       <c r="D95" t="n">
         <v>66.33131</v>
@@ -4051,7 +4051,7 @@
         <v>6.71004</v>
       </c>
       <c r="G95" t="n">
-        <v>190.6441</v>
+        <v>190.64407</v>
       </c>
       <c r="H95" t="n">
         <v>45.48</v>
@@ -4060,10 +4060,10 @@
         <v>44.53267</v>
       </c>
       <c r="J95" t="n">
-        <v>49.21491</v>
+        <v>49.21492</v>
       </c>
       <c r="K95" t="n">
-        <v>23.32524</v>
+        <v>23.32523</v>
       </c>
       <c r="L95" t="n">
         <v>2954.21997</v>
@@ -4074,10 +4074,10 @@
         <v>43891</v>
       </c>
       <c r="B96" t="n">
-        <v>61.3336</v>
+        <v>61.33359</v>
       </c>
       <c r="C96" t="n">
-        <v>149.20514</v>
+        <v>149.20512</v>
       </c>
       <c r="D96" t="n">
         <v>57.54987</v>
@@ -4089,7 +4089,7 @@
         <v>6.54929</v>
       </c>
       <c r="G96" t="n">
-        <v>165.21762</v>
+        <v>165.21761</v>
       </c>
       <c r="H96" t="n">
         <v>45.48</v>
@@ -4098,7 +4098,7 @@
         <v>34.93333</v>
       </c>
       <c r="J96" t="n">
-        <v>47.9739</v>
+        <v>47.97391</v>
       </c>
       <c r="K96" t="n">
         <v>20.63098</v>
@@ -4112,13 +4112,13 @@
         <v>43922</v>
       </c>
       <c r="B97" t="n">
-        <v>70.86323</v>
+        <v>70.86324999999999</v>
       </c>
       <c r="C97" t="n">
-        <v>169.54565</v>
+        <v>169.54573</v>
       </c>
       <c r="D97" t="n">
-        <v>66.7003</v>
+        <v>66.70029</v>
       </c>
       <c r="E97" t="n">
         <v>123.7</v>
@@ -4150,13 +4150,13 @@
         <v>43952</v>
       </c>
       <c r="B98" t="n">
-        <v>76.8933</v>
+        <v>76.89328</v>
       </c>
       <c r="C98" t="n">
-        <v>173.85068</v>
+        <v>173.85066</v>
       </c>
       <c r="D98" t="n">
-        <v>71.00037</v>
+        <v>71.00039</v>
       </c>
       <c r="E98" t="n">
         <v>122.1185</v>
@@ -4165,7 +4165,7 @@
         <v>8.820679999999999</v>
       </c>
       <c r="G98" t="n">
-        <v>222.95461</v>
+        <v>222.95462</v>
       </c>
       <c r="H98" t="n">
         <v>53.8</v>
@@ -4174,7 +4174,7 @@
         <v>55.66667</v>
       </c>
       <c r="J98" t="n">
-        <v>56.09852</v>
+        <v>56.09851</v>
       </c>
       <c r="K98" t="n">
         <v>25.34452</v>
@@ -4188,13 +4188,13 @@
         <v>43983</v>
       </c>
       <c r="B99" t="n">
-        <v>88.22629999999999</v>
+        <v>88.22631</v>
       </c>
       <c r="C99" t="n">
-        <v>193.07147</v>
+        <v>193.07149</v>
       </c>
       <c r="D99" t="n">
-        <v>70.23417999999999</v>
+        <v>70.23416</v>
       </c>
       <c r="E99" t="n">
         <v>137.94099</v>
@@ -4215,7 +4215,7 @@
         <v>53.33504</v>
       </c>
       <c r="K99" t="n">
-        <v>27.74537</v>
+        <v>27.74536</v>
       </c>
       <c r="L99" t="n">
         <v>3100.29004</v>
@@ -4229,10 +4229,10 @@
         <v>102.79526</v>
       </c>
       <c r="C100" t="n">
-        <v>194.49455</v>
+        <v>194.49454</v>
       </c>
       <c r="D100" t="n">
-        <v>73.69623</v>
+        <v>73.69624</v>
       </c>
       <c r="E100" t="n">
         <v>158.23399</v>
@@ -4241,7 +4241,7 @@
         <v>10.554</v>
       </c>
       <c r="G100" t="n">
-        <v>251.26349</v>
+        <v>251.26347</v>
       </c>
       <c r="H100" t="n">
         <v>77.43000000000001</v>
@@ -4253,7 +4253,7 @@
         <v>42.54858</v>
       </c>
       <c r="K100" t="n">
-        <v>27.84559</v>
+        <v>27.84558</v>
       </c>
       <c r="L100" t="n">
         <v>3271.12012</v>
@@ -4279,7 +4279,7 @@
         <v>13.29795</v>
       </c>
       <c r="G101" t="n">
-        <v>290.4184</v>
+        <v>290.41849</v>
       </c>
       <c r="H101" t="n">
         <v>90.81999999999999</v>
@@ -4302,13 +4302,13 @@
         <v>44075</v>
       </c>
       <c r="B102" t="n">
-        <v>112.23583</v>
+        <v>112.23584</v>
       </c>
       <c r="C102" t="n">
         <v>200.02402</v>
       </c>
       <c r="D102" t="n">
-        <v>72.58925000000001</v>
+        <v>72.58927</v>
       </c>
       <c r="E102" t="n">
         <v>157.43649</v>
@@ -4317,7 +4317,7 @@
         <v>13.45708</v>
       </c>
       <c r="G102" t="n">
-        <v>259.41537</v>
+        <v>259.41541</v>
       </c>
       <c r="H102" t="n">
         <v>81.98999999999999</v>
@@ -4329,7 +4329,7 @@
         <v>46.47241</v>
       </c>
       <c r="K102" t="n">
-        <v>32.31947</v>
+        <v>32.31946</v>
       </c>
       <c r="L102" t="n">
         <v>3363</v>
@@ -4340,10 +4340,10 @@
         <v>44105</v>
       </c>
       <c r="B103" t="n">
-        <v>105.50035</v>
+        <v>105.50034</v>
       </c>
       <c r="C103" t="n">
-        <v>192.54915</v>
+        <v>192.54916</v>
       </c>
       <c r="D103" t="n">
         <v>80.04382</v>
@@ -4355,7 +4355,7 @@
         <v>12.46599</v>
       </c>
       <c r="G103" t="n">
-        <v>260.61395</v>
+        <v>260.61386</v>
       </c>
       <c r="H103" t="n">
         <v>75.29000000000001</v>
@@ -4364,10 +4364,10 @@
         <v>129.34666</v>
       </c>
       <c r="J103" t="n">
-        <v>39.74119</v>
+        <v>39.74118</v>
       </c>
       <c r="K103" t="n">
-        <v>31.01629</v>
+        <v>31.0163</v>
       </c>
       <c r="L103" t="n">
         <v>3269.95996</v>
@@ -4393,7 +4393,7 @@
         <v>13.32878</v>
       </c>
       <c r="G104" t="n">
-        <v>274.34244</v>
+        <v>274.34247</v>
       </c>
       <c r="H104" t="n">
         <v>92.66</v>
@@ -4405,7 +4405,7 @@
         <v>43.70962</v>
       </c>
       <c r="K104" t="n">
-        <v>35.62488</v>
+        <v>35.62487</v>
       </c>
       <c r="L104" t="n">
         <v>3621.62988</v>
@@ -4416,10 +4416,10 @@
         <v>44166</v>
       </c>
       <c r="B105" t="n">
-        <v>128.81676</v>
+        <v>128.81674</v>
       </c>
       <c r="C105" t="n">
-        <v>212.07539</v>
+        <v>212.07535</v>
       </c>
       <c r="D105" t="n">
         <v>86.80598000000001</v>
@@ -4431,7 +4431,7 @@
         <v>12.988</v>
       </c>
       <c r="G105" t="n">
-        <v>270.56854</v>
+        <v>270.56857</v>
       </c>
       <c r="H105" t="n">
         <v>91.70999999999999</v>
@@ -4454,13 +4454,13 @@
         <v>44197</v>
       </c>
       <c r="B106" t="n">
-        <v>128.10808</v>
+        <v>128.10809</v>
       </c>
       <c r="C106" t="n">
         <v>221.17168</v>
       </c>
       <c r="D106" t="n">
-        <v>90.50677</v>
+        <v>90.50676</v>
       </c>
       <c r="E106" t="n">
         <v>160.31</v>
@@ -4469,7 +4469,7 @@
         <v>12.92308</v>
       </c>
       <c r="G106" t="n">
-        <v>255.87924</v>
+        <v>255.87926</v>
       </c>
       <c r="H106" t="n">
         <v>85.64</v>
@@ -4481,7 +4481,7 @@
         <v>50.18244</v>
       </c>
       <c r="K106" t="n">
-        <v>40.30519</v>
+        <v>40.30517</v>
       </c>
       <c r="L106" t="n">
         <v>3714.23999</v>
@@ -4498,7 +4498,7 @@
         <v>222.08249</v>
       </c>
       <c r="D107" t="n">
-        <v>100.14256</v>
+        <v>100.14257</v>
       </c>
       <c r="E107" t="n">
         <v>154.6465</v>
@@ -4530,10 +4530,10 @@
         <v>44256</v>
       </c>
       <c r="B108" t="n">
-        <v>118.76163</v>
+        <v>118.76162</v>
       </c>
       <c r="C108" t="n">
-        <v>225.32225</v>
+        <v>225.32228</v>
       </c>
       <c r="D108" t="n">
         <v>102.15394</v>
@@ -4545,7 +4545,7 @@
         <v>13.28433</v>
       </c>
       <c r="G108" t="n">
-        <v>291.73581</v>
+        <v>291.73587</v>
       </c>
       <c r="H108" t="n">
         <v>78.5</v>
@@ -4568,7 +4568,7 @@
         <v>44287</v>
       </c>
       <c r="B109" t="n">
-        <v>127.81338</v>
+        <v>127.81342</v>
       </c>
       <c r="C109" t="n">
         <v>241.00505</v>
@@ -4583,7 +4583,7 @@
         <v>14.93762</v>
       </c>
       <c r="G109" t="n">
-        <v>321.99603</v>
+        <v>321.99594</v>
       </c>
       <c r="H109" t="n">
         <v>81.62</v>
@@ -4592,7 +4592,7 @@
         <v>236.48</v>
       </c>
       <c r="J109" t="n">
-        <v>52.32426</v>
+        <v>52.32427</v>
       </c>
       <c r="K109" t="n">
         <v>41.13419</v>
@@ -4606,19 +4606,19 @@
         <v>44317</v>
       </c>
       <c r="B110" t="n">
-        <v>121.35917</v>
+        <v>121.35918</v>
       </c>
       <c r="C110" t="n">
         <v>239.16684</v>
       </c>
       <c r="D110" t="n">
-        <v>116.73171</v>
+        <v>116.73172</v>
       </c>
       <c r="E110" t="n">
         <v>161.1535</v>
       </c>
       <c r="F110" t="n">
-        <v>16.1667</v>
+        <v>16.16671</v>
       </c>
       <c r="G110" t="n">
         <v>325.61139</v>
@@ -4644,22 +4644,22 @@
         <v>44348</v>
       </c>
       <c r="B111" t="n">
-        <v>133.38696</v>
+        <v>133.38699</v>
       </c>
       <c r="C111" t="n">
-        <v>259.49332</v>
+        <v>259.49338</v>
       </c>
       <c r="D111" t="n">
-        <v>120.93869</v>
+        <v>120.93868</v>
       </c>
       <c r="E111" t="n">
         <v>172.008</v>
       </c>
       <c r="F111" t="n">
-        <v>19.91127</v>
+        <v>19.91128</v>
       </c>
       <c r="G111" t="n">
-        <v>344.41132</v>
+        <v>344.41135</v>
       </c>
       <c r="H111" t="n">
         <v>93.93000000000001</v>
@@ -4671,7 +4671,7 @@
         <v>51.37452</v>
       </c>
       <c r="K111" t="n">
-        <v>43.33179</v>
+        <v>43.33178</v>
       </c>
       <c r="L111" t="n">
         <v>4297.5</v>
@@ -4688,13 +4688,13 @@
         <v>272.91345</v>
       </c>
       <c r="D112" t="n">
-        <v>133.45659</v>
+        <v>133.45657</v>
       </c>
       <c r="E112" t="n">
         <v>166.3795</v>
       </c>
       <c r="F112" t="n">
-        <v>19.41006</v>
+        <v>19.41007</v>
       </c>
       <c r="G112" t="n">
         <v>352.91983</v>
@@ -4706,7 +4706,7 @@
         <v>229.06667</v>
       </c>
       <c r="J112" t="n">
-        <v>49.15994</v>
+        <v>49.15995</v>
       </c>
       <c r="K112" t="n">
         <v>44.10966</v>
@@ -4723,7 +4723,7 @@
         <v>148.09059</v>
       </c>
       <c r="C113" t="n">
-        <v>289.72247</v>
+        <v>289.72241</v>
       </c>
       <c r="D113" t="n">
         <v>143.33357</v>
@@ -4735,7 +4735,7 @@
         <v>22.28683</v>
       </c>
       <c r="G113" t="n">
-        <v>375.78094</v>
+        <v>375.78088</v>
       </c>
       <c r="H113" t="n">
         <v>110.72</v>
@@ -4758,7 +4758,7 @@
         <v>44440</v>
       </c>
       <c r="B114" t="n">
-        <v>138.01501</v>
+        <v>138.01503</v>
       </c>
       <c r="C114" t="n">
         <v>270.56631</v>
@@ -4770,10 +4770,10 @@
         <v>164.252</v>
       </c>
       <c r="F114" t="n">
-        <v>20.62515</v>
+        <v>20.62516</v>
       </c>
       <c r="G114" t="n">
-        <v>336.17026</v>
+        <v>336.17032</v>
       </c>
       <c r="H114" t="n">
         <v>102.9</v>
@@ -4782,10 +4782,10 @@
         <v>258.49335</v>
       </c>
       <c r="J114" t="n">
-        <v>49.07413</v>
+        <v>49.07414</v>
       </c>
       <c r="K114" t="n">
-        <v>44.3899</v>
+        <v>44.38989</v>
       </c>
       <c r="L114" t="n">
         <v>4307.54004</v>
@@ -4796,22 +4796,22 @@
         <v>44470</v>
       </c>
       <c r="B115" t="n">
-        <v>146.1106</v>
+        <v>146.11058</v>
       </c>
       <c r="C115" t="n">
-        <v>318.26468</v>
+        <v>318.26477</v>
       </c>
       <c r="D115" t="n">
-        <v>146.65053</v>
+        <v>146.65054</v>
       </c>
       <c r="E115" t="n">
         <v>168.62151</v>
       </c>
       <c r="F115" t="n">
-        <v>25.45489</v>
+        <v>25.45488</v>
       </c>
       <c r="G115" t="n">
-        <v>320.50037</v>
+        <v>320.50034</v>
       </c>
       <c r="H115" t="n">
         <v>120.23</v>
@@ -4820,7 +4820,7 @@
         <v>371.33334</v>
       </c>
       <c r="J115" t="n">
-        <v>45.132</v>
+        <v>45.13199</v>
       </c>
       <c r="K115" t="n">
         <v>48.66842</v>
@@ -4834,13 +4834,13 @@
         <v>44501</v>
       </c>
       <c r="B116" t="n">
-        <v>161.46414</v>
+        <v>161.46416</v>
       </c>
       <c r="C116" t="n">
-        <v>317.85666</v>
+        <v>317.85672</v>
       </c>
       <c r="D116" t="n">
-        <v>140.55998</v>
+        <v>140.55997</v>
       </c>
       <c r="E116" t="n">
         <v>175.3535</v>
@@ -4849,7 +4849,7 @@
         <v>32.5327</v>
       </c>
       <c r="G116" t="n">
-        <v>321.38193</v>
+        <v>321.38187</v>
       </c>
       <c r="H116" t="n">
         <v>158.37</v>
@@ -4861,7 +4861,7 @@
         <v>45.63135</v>
       </c>
       <c r="K116" t="n">
-        <v>50.6832</v>
+        <v>50.68319</v>
       </c>
       <c r="L116" t="n">
         <v>4567</v>
@@ -4872,13 +4872,13 @@
         <v>44531</v>
       </c>
       <c r="B117" t="n">
-        <v>173.44945</v>
+        <v>173.44946</v>
       </c>
       <c r="C117" t="n">
-        <v>323.36597</v>
+        <v>323.36594</v>
       </c>
       <c r="D117" t="n">
-        <v>143.48663</v>
+        <v>143.48665</v>
       </c>
       <c r="E117" t="n">
         <v>166.717</v>
@@ -4887,7 +4887,7 @@
         <v>29.28561</v>
       </c>
       <c r="G117" t="n">
-        <v>333.15909</v>
+        <v>333.15906</v>
       </c>
       <c r="H117" t="n">
         <v>143.89999</v>
@@ -4899,7 +4899,7 @@
         <v>47.76452</v>
       </c>
       <c r="K117" t="n">
-        <v>61.30046</v>
+        <v>61.30047</v>
       </c>
       <c r="L117" t="n">
         <v>4766.18018</v>
@@ -4910,10 +4910,10 @@
         <v>44562</v>
       </c>
       <c r="B118" t="n">
-        <v>170.72417</v>
+        <v>170.72414</v>
       </c>
       <c r="C118" t="n">
-        <v>299.00195</v>
+        <v>299.00208</v>
       </c>
       <c r="D118" t="n">
         <v>134.02812</v>
@@ -4925,7 +4925,7 @@
         <v>24.38161</v>
       </c>
       <c r="G118" t="n">
-        <v>310.28815</v>
+        <v>310.28818</v>
       </c>
       <c r="H118" t="n">
         <v>114.25</v>
@@ -4934,10 +4934,10 @@
         <v>312.23999</v>
       </c>
       <c r="J118" t="n">
-        <v>45.27891</v>
+        <v>45.2789</v>
       </c>
       <c r="K118" t="n">
-        <v>53.97383</v>
+        <v>53.97382</v>
       </c>
       <c r="L118" t="n">
         <v>4515.5498</v>
@@ -4951,10 +4951,10 @@
         <v>161.49379</v>
       </c>
       <c r="C119" t="n">
-        <v>287.87552</v>
+        <v>287.87549</v>
       </c>
       <c r="D119" t="n">
-        <v>133.78397</v>
+        <v>133.78394</v>
       </c>
       <c r="E119" t="n">
         <v>153.563</v>
@@ -4963,7 +4963,7 @@
         <v>24.28104</v>
       </c>
       <c r="G119" t="n">
-        <v>209.02797</v>
+        <v>209.028</v>
       </c>
       <c r="H119" t="n">
         <v>123.34</v>
@@ -4972,7 +4972,7 @@
         <v>290.14334</v>
       </c>
       <c r="J119" t="n">
-        <v>44.57715</v>
+        <v>44.57716</v>
       </c>
       <c r="K119" t="n">
         <v>54.11753</v>
@@ -4986,13 +4986,13 @@
         <v>44621</v>
       </c>
       <c r="B120" t="n">
-        <v>170.77545</v>
+        <v>170.77542</v>
       </c>
       <c r="C120" t="n">
         <v>297.04782</v>
       </c>
       <c r="D120" t="n">
-        <v>137.75664</v>
+        <v>137.75665</v>
       </c>
       <c r="E120" t="n">
         <v>162.9975</v>
@@ -5001,7 +5001,7 @@
         <v>27.1743</v>
       </c>
       <c r="G120" t="n">
-        <v>220.2505</v>
+        <v>220.25053</v>
       </c>
       <c r="H120" t="n">
         <v>109.34</v>
@@ -5027,7 +5027,7 @@
         <v>154.18785</v>
       </c>
       <c r="C121" t="n">
-        <v>267.38248</v>
+        <v>267.3826</v>
       </c>
       <c r="D121" t="n">
         <v>113.03391</v>
@@ -5036,7 +5036,7 @@
         <v>124.2815</v>
       </c>
       <c r="F121" t="n">
-        <v>18.47107</v>
+        <v>18.47108</v>
       </c>
       <c r="G121" t="n">
         <v>198.56818</v>
@@ -5048,10 +5048,10 @@
         <v>290.25333</v>
       </c>
       <c r="J121" t="n">
-        <v>40.73623</v>
+        <v>40.73622</v>
       </c>
       <c r="K121" t="n">
-        <v>51.41818</v>
+        <v>51.41819</v>
       </c>
       <c r="L121" t="n">
         <v>4131.93018</v>
@@ -5062,7 +5062,7 @@
         <v>44682</v>
       </c>
       <c r="B122" t="n">
-        <v>145.78522</v>
+        <v>145.7852</v>
       </c>
       <c r="C122" t="n">
         <v>262.54901</v>
@@ -5074,10 +5074,10 @@
         <v>120.2095</v>
       </c>
       <c r="F122" t="n">
-        <v>18.59556</v>
+        <v>18.59557</v>
       </c>
       <c r="G122" t="n">
-        <v>191.80295</v>
+        <v>191.80298</v>
       </c>
       <c r="H122" t="n">
         <v>101.86</v>
@@ -5103,7 +5103,7 @@
         <v>133.91397</v>
       </c>
       <c r="C123" t="n">
-        <v>248.0246</v>
+        <v>248.02464</v>
       </c>
       <c r="D123" t="n">
         <v>107.93591</v>
@@ -5112,10 +5112,10 @@
         <v>106.21</v>
       </c>
       <c r="F123" t="n">
-        <v>15.10014</v>
+        <v>15.10013</v>
       </c>
       <c r="G123" t="n">
-        <v>159.72026</v>
+        <v>159.72021</v>
       </c>
       <c r="H123" t="n">
         <v>76.47</v>
@@ -5124,10 +5124,10 @@
         <v>224.47333</v>
       </c>
       <c r="J123" t="n">
-        <v>35.23718</v>
+        <v>35.23719</v>
       </c>
       <c r="K123" t="n">
-        <v>45.43113</v>
+        <v>45.43112</v>
       </c>
       <c r="L123" t="n">
         <v>3785.37988</v>
@@ -5138,13 +5138,13 @@
         <v>44743</v>
       </c>
       <c r="B124" t="n">
-        <v>159.17465</v>
+        <v>159.17468</v>
       </c>
       <c r="C124" t="n">
-        <v>271.1149</v>
+        <v>271.11487</v>
       </c>
       <c r="D124" t="n">
-        <v>115.22356</v>
+        <v>115.22357</v>
       </c>
       <c r="E124" t="n">
         <v>134.95</v>
@@ -5153,7 +5153,7 @@
         <v>18.09247</v>
       </c>
       <c r="G124" t="n">
-        <v>157.59065</v>
+        <v>157.59067</v>
       </c>
       <c r="H124" t="n">
         <v>94.47</v>
@@ -5165,7 +5165,7 @@
         <v>34.20107</v>
       </c>
       <c r="K124" t="n">
-        <v>50.07607</v>
+        <v>50.07608</v>
       </c>
       <c r="L124" t="n">
         <v>4130.29004</v>
@@ -5176,13 +5176,13 @@
         <v>44774</v>
       </c>
       <c r="B125" t="n">
-        <v>154.20714</v>
+        <v>154.20717</v>
       </c>
       <c r="C125" t="n">
-        <v>253.04153</v>
+        <v>253.04149</v>
       </c>
       <c r="D125" t="n">
-        <v>107.19992</v>
+        <v>107.19991</v>
       </c>
       <c r="E125" t="n">
         <v>126.77</v>
@@ -5191,7 +5191,7 @@
         <v>15.03539</v>
       </c>
       <c r="G125" t="n">
-        <v>161.38429</v>
+        <v>161.38432</v>
       </c>
       <c r="H125" t="n">
         <v>84.87</v>
@@ -5200,10 +5200,10 @@
         <v>275.60999</v>
       </c>
       <c r="J125" t="n">
-        <v>30.36957</v>
+        <v>30.36958</v>
       </c>
       <c r="K125" t="n">
-        <v>46.67488</v>
+        <v>46.67489</v>
       </c>
       <c r="L125" t="n">
         <v>3955</v>
@@ -5214,13 +5214,13 @@
         <v>44805</v>
       </c>
       <c r="B126" t="n">
-        <v>135.55165</v>
+        <v>135.55157</v>
       </c>
       <c r="C126" t="n">
-        <v>225.39246</v>
+        <v>225.39247</v>
       </c>
       <c r="D126" t="n">
-        <v>94.7484</v>
+        <v>94.74841000000001</v>
       </c>
       <c r="E126" t="n">
         <v>113</v>
@@ -5238,10 +5238,10 @@
         <v>265.25</v>
       </c>
       <c r="J126" t="n">
-        <v>24.5183</v>
+        <v>24.51829</v>
       </c>
       <c r="K126" t="n">
-        <v>41.87031</v>
+        <v>41.8703</v>
       </c>
       <c r="L126" t="n">
         <v>3585.62012</v>
@@ -5252,10 +5252,10 @@
         <v>44835</v>
       </c>
       <c r="B127" t="n">
-        <v>150.40149</v>
+        <v>150.4015</v>
       </c>
       <c r="C127" t="n">
-        <v>224.64729</v>
+        <v>224.64731</v>
       </c>
       <c r="D127" t="n">
         <v>93.61915999999999</v>
@@ -5276,10 +5276,10 @@
         <v>227.53999</v>
       </c>
       <c r="J127" t="n">
-        <v>27.0491</v>
+        <v>27.04909</v>
       </c>
       <c r="K127" t="n">
-        <v>44.3325</v>
+        <v>44.33249</v>
       </c>
       <c r="L127" t="n">
         <v>3871.97998</v>
@@ -5290,13 +5290,13 @@
         <v>44866</v>
       </c>
       <c r="B128" t="n">
-        <v>145.43414</v>
+        <v>145.4341</v>
       </c>
       <c r="C128" t="n">
-        <v>247.6114</v>
+        <v>247.61142</v>
       </c>
       <c r="D128" t="n">
-        <v>100.03807</v>
+        <v>100.03806</v>
       </c>
       <c r="E128" t="n">
         <v>96.54000000000001</v>
@@ -5305,7 +5305,7 @@
         <v>16.86661</v>
       </c>
       <c r="G128" t="n">
-        <v>116.97959</v>
+        <v>116.9796</v>
       </c>
       <c r="H128" t="n">
         <v>77.63</v>
@@ -5331,7 +5331,7 @@
         <v>127.6515</v>
       </c>
       <c r="C129" t="n">
-        <v>232.74352</v>
+        <v>232.74348</v>
       </c>
       <c r="D129" t="n">
         <v>87.39834999999999</v>
@@ -5355,7 +5355,7 @@
         <v>25.48586</v>
       </c>
       <c r="K129" t="n">
-        <v>53.16611</v>
+        <v>53.1661</v>
       </c>
       <c r="L129" t="n">
         <v>3839.5</v>
@@ -5366,13 +5366,13 @@
         <v>44927</v>
       </c>
       <c r="B130" t="n">
-        <v>141.75967</v>
+        <v>141.7597</v>
       </c>
       <c r="C130" t="n">
         <v>240.49774</v>
       </c>
       <c r="D130" t="n">
-        <v>97.90832</v>
+        <v>97.90833000000001</v>
       </c>
       <c r="E130" t="n">
         <v>103.13</v>
@@ -5404,10 +5404,10 @@
         <v>44958</v>
       </c>
       <c r="B131" t="n">
-        <v>145.0461</v>
+        <v>145.04611</v>
       </c>
       <c r="C131" t="n">
-        <v>242.6665</v>
+        <v>242.66649</v>
       </c>
       <c r="D131" t="n">
         <v>89.21108</v>
@@ -5419,7 +5419,7 @@
         <v>23.13864</v>
       </c>
       <c r="G131" t="n">
-        <v>173.28036</v>
+        <v>173.28038</v>
       </c>
       <c r="H131" t="n">
         <v>78.58</v>
@@ -5428,7 +5428,7 @@
         <v>205.71001</v>
       </c>
       <c r="J131" t="n">
-        <v>24.33236</v>
+        <v>24.33237</v>
       </c>
       <c r="K131" t="n">
         <v>56.50938</v>
@@ -5442,13 +5442,13 @@
         <v>44986</v>
       </c>
       <c r="B132" t="n">
-        <v>162.25563</v>
+        <v>162.25565</v>
       </c>
       <c r="C132" t="n">
-        <v>280.49371</v>
+        <v>280.49374</v>
       </c>
       <c r="D132" t="n">
-        <v>102.75224</v>
+        <v>102.75223</v>
       </c>
       <c r="E132" t="n">
         <v>103.29</v>
@@ -5469,7 +5469,7 @@
         <v>31.88681</v>
       </c>
       <c r="K132" t="n">
-        <v>61.4413</v>
+        <v>61.44131</v>
       </c>
       <c r="L132" t="n">
         <v>4109.31006</v>
@@ -5480,22 +5480,22 @@
         <v>45017</v>
       </c>
       <c r="B133" t="n">
-        <v>166.95897</v>
+        <v>166.95898</v>
       </c>
       <c r="C133" t="n">
-        <v>298.94037</v>
+        <v>298.94034</v>
       </c>
       <c r="D133" t="n">
-        <v>106.32821</v>
+        <v>106.3282</v>
       </c>
       <c r="E133" t="n">
         <v>105.45</v>
       </c>
       <c r="F133" t="n">
-        <v>27.66124</v>
+        <v>27.66123</v>
       </c>
       <c r="G133" t="n">
-        <v>238.04012</v>
+        <v>238.04013</v>
       </c>
       <c r="H133" t="n">
         <v>89.37</v>
@@ -5507,7 +5507,7 @@
         <v>30.31541</v>
       </c>
       <c r="K133" t="n">
-        <v>60.00091</v>
+        <v>60.0009</v>
       </c>
       <c r="L133" t="n">
         <v>4169.47998</v>
@@ -5524,16 +5524,16 @@
         <v>320.19669</v>
       </c>
       <c r="D134" t="n">
-        <v>121.71183</v>
+        <v>121.71184</v>
       </c>
       <c r="E134" t="n">
         <v>120.58</v>
       </c>
       <c r="F134" t="n">
-        <v>37.71432</v>
+        <v>37.71433</v>
       </c>
       <c r="G134" t="n">
-        <v>262.20862</v>
+        <v>262.20865</v>
       </c>
       <c r="H134" t="n">
         <v>118.21</v>
@@ -5545,7 +5545,7 @@
         <v>30.81196</v>
       </c>
       <c r="K134" t="n">
-        <v>77.37962</v>
+        <v>77.37961</v>
       </c>
       <c r="L134" t="n">
         <v>4179.83008</v>
@@ -5556,22 +5556,22 @@
         <v>45078</v>
       </c>
       <c r="B135" t="n">
-        <v>191.12346</v>
+        <v>191.12347</v>
       </c>
       <c r="C135" t="n">
         <v>332.04349</v>
       </c>
       <c r="D135" t="n">
-        <v>118.57171</v>
+        <v>118.5717</v>
       </c>
       <c r="E135" t="n">
         <v>130.36</v>
       </c>
       <c r="F135" t="n">
-        <v>42.17256</v>
+        <v>42.17257</v>
       </c>
       <c r="G135" t="n">
-        <v>284.25754</v>
+        <v>284.25745</v>
       </c>
       <c r="H135" t="n">
         <v>113.91</v>
@@ -5583,7 +5583,7 @@
         <v>32.77201</v>
       </c>
       <c r="K135" t="n">
-        <v>83.51774</v>
+        <v>83.51775000000001</v>
       </c>
       <c r="L135" t="n">
         <v>4450.37988</v>
@@ -5594,10 +5594,10 @@
         <v>45108</v>
       </c>
       <c r="B136" t="n">
-        <v>193.56705</v>
+        <v>193.56706</v>
       </c>
       <c r="C136" t="n">
-        <v>327.53888</v>
+        <v>327.53885</v>
       </c>
       <c r="D136" t="n">
         <v>131.46898</v>
@@ -5606,10 +5606,10 @@
         <v>133.67999</v>
       </c>
       <c r="F136" t="n">
-        <v>46.58601</v>
+        <v>46.58602</v>
       </c>
       <c r="G136" t="n">
-        <v>315.57751</v>
+        <v>315.57748</v>
       </c>
       <c r="H136" t="n">
         <v>114.4</v>
@@ -5621,7 +5621,7 @@
         <v>35.05547</v>
       </c>
       <c r="K136" t="n">
-        <v>86.52366000000001</v>
+        <v>86.52367</v>
       </c>
       <c r="L136" t="n">
         <v>4588.95996</v>
@@ -5638,7 +5638,7 @@
         <v>320.25903</v>
       </c>
       <c r="D137" t="n">
-        <v>134.88647</v>
+        <v>134.88646</v>
       </c>
       <c r="E137" t="n">
         <v>138.00999</v>
@@ -5647,7 +5647,7 @@
         <v>49.20398</v>
       </c>
       <c r="G137" t="n">
-        <v>293.08301</v>
+        <v>293.08298</v>
       </c>
       <c r="H137" t="n">
         <v>105.72</v>
@@ -5670,22 +5670,22 @@
         <v>45170</v>
       </c>
       <c r="B138" t="n">
-        <v>168.92529</v>
+        <v>168.92528</v>
       </c>
       <c r="C138" t="n">
-        <v>308.52386</v>
+        <v>308.52383</v>
       </c>
       <c r="D138" t="n">
-        <v>129.6265</v>
+        <v>129.62651</v>
       </c>
       <c r="E138" t="n">
         <v>127.12</v>
       </c>
       <c r="F138" t="n">
-        <v>43.36947</v>
+        <v>43.36948</v>
       </c>
       <c r="G138" t="n">
-        <v>297.36197</v>
+        <v>297.362</v>
       </c>
       <c r="H138" t="n">
         <v>102.82</v>
@@ -5694,7 +5694,7 @@
         <v>250.22</v>
       </c>
       <c r="J138" t="n">
-        <v>34.96521</v>
+        <v>34.9652</v>
       </c>
       <c r="K138" t="n">
         <v>80.4053</v>
@@ -5708,13 +5708,13 @@
         <v>45200</v>
       </c>
       <c r="B139" t="n">
-        <v>168.49115</v>
+        <v>168.49113</v>
       </c>
       <c r="C139" t="n">
         <v>330.37213</v>
       </c>
       <c r="D139" t="n">
-        <v>122.91042</v>
+        <v>122.91043</v>
       </c>
       <c r="E139" t="n">
         <v>133.09</v>
@@ -5723,7 +5723,7 @@
         <v>40.65857</v>
       </c>
       <c r="G139" t="n">
-        <v>298.4119</v>
+        <v>298.41183</v>
       </c>
       <c r="H139" t="n">
         <v>98.5</v>
@@ -5746,22 +5746,22 @@
         <v>45231</v>
       </c>
       <c r="B140" t="n">
-        <v>187.66206</v>
+        <v>187.66209</v>
       </c>
       <c r="C140" t="n">
         <v>370.9899</v>
       </c>
       <c r="D140" t="n">
-        <v>131.28076</v>
+        <v>131.28078</v>
       </c>
       <c r="E140" t="n">
         <v>146.09</v>
       </c>
       <c r="F140" t="n">
-        <v>46.63072</v>
+        <v>46.63073</v>
       </c>
       <c r="G140" t="n">
-        <v>324.04645</v>
+        <v>324.04636</v>
       </c>
       <c r="H140" t="n">
         <v>121.16</v>
@@ -5784,13 +5784,13 @@
         <v>45261</v>
       </c>
       <c r="B141" t="n">
-        <v>190.21103</v>
+        <v>190.21104</v>
       </c>
       <c r="C141" t="n">
-        <v>368.1799</v>
+        <v>368.17987</v>
       </c>
       <c r="D141" t="n">
-        <v>138.37328</v>
+        <v>138.37329</v>
       </c>
       <c r="E141" t="n">
         <v>151.94</v>
@@ -5799,7 +5799,7 @@
         <v>49.37888</v>
       </c>
       <c r="G141" t="n">
-        <v>350.60202</v>
+        <v>350.60199</v>
       </c>
       <c r="H141" t="n">
         <v>147.41</v>
@@ -5811,7 +5811,7 @@
         <v>49.5859</v>
       </c>
       <c r="K141" t="n">
-        <v>108.55682</v>
+        <v>108.55681</v>
       </c>
       <c r="L141" t="n">
         <v>4769.83008</v>
@@ -5822,13 +5822,13 @@
         <v>45292</v>
       </c>
       <c r="B142" t="n">
-        <v>182.17892</v>
+        <v>182.17896</v>
       </c>
       <c r="C142" t="n">
-        <v>389.26971</v>
+        <v>389.26962</v>
       </c>
       <c r="D142" t="n">
-        <v>138.77942</v>
+        <v>138.77943</v>
       </c>
       <c r="E142" t="n">
         <v>155.2</v>
@@ -5860,13 +5860,13 @@
         <v>45323</v>
       </c>
       <c r="B143" t="n">
-        <v>178.80078</v>
+        <v>178.80077</v>
       </c>
       <c r="C143" t="n">
         <v>405.74286</v>
       </c>
       <c r="D143" t="n">
-        <v>137.15489</v>
+        <v>137.15488</v>
       </c>
       <c r="E143" t="n">
         <v>176.75999</v>
@@ -5875,7 +5875,7 @@
         <v>78.88334999999999</v>
       </c>
       <c r="G143" t="n">
-        <v>485.9953</v>
+        <v>485.99533</v>
       </c>
       <c r="H143" t="n">
         <v>192.53</v>
@@ -5904,7 +5904,7 @@
         <v>412.68771</v>
       </c>
       <c r="D144" t="n">
-        <v>149.50734</v>
+        <v>149.50732</v>
       </c>
       <c r="E144" t="n">
         <v>180.38</v>
@@ -5913,7 +5913,7 @@
         <v>90.09911</v>
       </c>
       <c r="G144" t="n">
-        <v>481.4837</v>
+        <v>481.48367</v>
       </c>
       <c r="H144" t="n">
         <v>180.49001</v>
@@ -5925,7 +5925,7 @@
         <v>43.71401</v>
       </c>
       <c r="K144" t="n">
-        <v>129.44682</v>
+        <v>129.44685</v>
       </c>
       <c r="L144" t="n">
         <v>5254.3501</v>
@@ -5939,19 +5939,19 @@
         <v>168.49315</v>
       </c>
       <c r="C145" t="n">
-        <v>381.89694</v>
+        <v>381.89697</v>
       </c>
       <c r="D145" t="n">
-        <v>161.24564</v>
+        <v>161.24562</v>
       </c>
       <c r="E145" t="n">
         <v>175</v>
       </c>
       <c r="F145" t="n">
-        <v>86.15634</v>
+        <v>86.15633</v>
       </c>
       <c r="G145" t="n">
-        <v>426.54114</v>
+        <v>426.54117</v>
       </c>
       <c r="H145" t="n">
         <v>158.38</v>
@@ -5974,13 +5974,13 @@
         <v>45413</v>
       </c>
       <c r="B146" t="n">
-        <v>190.43472</v>
+        <v>190.43471</v>
       </c>
       <c r="C146" t="n">
         <v>407.93893</v>
       </c>
       <c r="D146" t="n">
-        <v>170.87402</v>
+        <v>170.87401</v>
       </c>
       <c r="E146" t="n">
         <v>176.44</v>
@@ -5989,7 +5989,7 @@
         <v>109.3213</v>
       </c>
       <c r="G146" t="n">
-        <v>462.89185</v>
+        <v>462.89182</v>
       </c>
       <c r="H146" t="n">
         <v>166.89999</v>
@@ -6001,7 +6001,7 @@
         <v>30.65553</v>
       </c>
       <c r="K146" t="n">
-        <v>129.75349</v>
+        <v>129.75352</v>
       </c>
       <c r="L146" t="n">
         <v>5277.50977</v>
@@ -6018,16 +6018,16 @@
         <v>439.2077</v>
       </c>
       <c r="D147" t="n">
-        <v>180.64015</v>
+        <v>180.64014</v>
       </c>
       <c r="E147" t="n">
         <v>193.25</v>
       </c>
       <c r="F147" t="n">
-        <v>123.19888</v>
+        <v>123.19886</v>
       </c>
       <c r="G147" t="n">
-        <v>500.46283</v>
+        <v>500.46286</v>
       </c>
       <c r="H147" t="n">
         <v>162.21001</v>
@@ -6039,7 +6039,7 @@
         <v>30.77478</v>
       </c>
       <c r="K147" t="n">
-        <v>157.30281</v>
+        <v>157.3028</v>
       </c>
       <c r="L147" t="n">
         <v>5460.47998</v>
@@ -6053,19 +6053,19 @@
         <v>219.98305</v>
       </c>
       <c r="C148" t="n">
-        <v>411.10312</v>
+        <v>411.10315</v>
       </c>
       <c r="D148" t="n">
-        <v>170.11809</v>
+        <v>170.11806</v>
       </c>
       <c r="E148" t="n">
         <v>186.98</v>
       </c>
       <c r="F148" t="n">
-        <v>116.69685</v>
+        <v>116.69686</v>
       </c>
       <c r="G148" t="n">
-        <v>471.29187</v>
+        <v>471.29184</v>
       </c>
       <c r="H148" t="n">
         <v>144.48</v>
@@ -6094,16 +6094,16 @@
         <v>410.65292</v>
       </c>
       <c r="D149" t="n">
-        <v>162.02573</v>
+        <v>162.02574</v>
       </c>
       <c r="E149" t="n">
         <v>178.5</v>
       </c>
       <c r="F149" t="n">
-        <v>119.04037</v>
+        <v>119.04038</v>
       </c>
       <c r="G149" t="n">
-        <v>517.4256</v>
+        <v>517.42548</v>
       </c>
       <c r="H149" t="n">
         <v>148.56</v>
@@ -6115,7 +6115,7 @@
         <v>22.04</v>
       </c>
       <c r="K149" t="n">
-        <v>159.52394</v>
+        <v>159.52393</v>
       </c>
       <c r="L149" t="n">
         <v>5648.3999</v>
@@ -6126,19 +6126,19 @@
         <v>45536</v>
       </c>
       <c r="B150" t="n">
-        <v>231.06708</v>
+        <v>231.06705</v>
       </c>
       <c r="C150" t="n">
         <v>423.60825</v>
       </c>
       <c r="D150" t="n">
-        <v>164.6935</v>
+        <v>164.69351</v>
       </c>
       <c r="E150" t="n">
         <v>186.33</v>
       </c>
       <c r="F150" t="n">
-        <v>121.11504</v>
+        <v>121.11502</v>
       </c>
       <c r="G150" t="n">
         <v>568.71655</v>
@@ -6164,19 +6164,19 @@
         <v>45566</v>
       </c>
       <c r="B151" t="n">
-        <v>224.0359</v>
+        <v>224.03589</v>
       </c>
       <c r="C151" t="n">
-        <v>400.03073</v>
+        <v>400.03067</v>
       </c>
       <c r="D151" t="n">
-        <v>169.91681</v>
+        <v>169.91684</v>
       </c>
       <c r="E151" t="n">
         <v>186.39999</v>
       </c>
       <c r="F151" t="n">
-        <v>132.40471</v>
+        <v>132.40472</v>
       </c>
       <c r="G151" t="n">
         <v>563.88818</v>
@@ -6191,7 +6191,7 @@
         <v>21.52</v>
       </c>
       <c r="K151" t="n">
-        <v>166.88029</v>
+        <v>166.88031</v>
       </c>
       <c r="L151" t="n">
         <v>5705.4502</v>
@@ -6229,7 +6229,7 @@
         <v>24.05</v>
       </c>
       <c r="K152" t="n">
-        <v>159.3212</v>
+        <v>159.32121</v>
       </c>
       <c r="L152" t="n">
         <v>6032.37988</v>
@@ -6246,16 +6246,16 @@
         <v>415.77573</v>
       </c>
       <c r="D153" t="n">
-        <v>188.1954</v>
+        <v>188.19543</v>
       </c>
       <c r="E153" t="n">
         <v>219.39</v>
       </c>
       <c r="F153" t="n">
-        <v>133.93987</v>
+        <v>133.93983</v>
       </c>
       <c r="G153" t="n">
-        <v>582.17078</v>
+        <v>582.17084</v>
       </c>
       <c r="H153" t="n">
         <v>120.79</v>
@@ -6267,7 +6267,7 @@
         <v>20.05</v>
       </c>
       <c r="K153" t="n">
-        <v>228.50441</v>
+        <v>228.50439</v>
       </c>
       <c r="L153" t="n">
         <v>5881.62988</v>
@@ -6278,13 +6278,13 @@
         <v>45658</v>
       </c>
       <c r="B154" t="n">
-        <v>234.29968</v>
+        <v>234.29967</v>
       </c>
       <c r="C154" t="n">
-        <v>409.42319</v>
+        <v>409.42313</v>
       </c>
       <c r="D154" t="n">
-        <v>202.82953</v>
+        <v>202.82951</v>
       </c>
       <c r="E154" t="n">
         <v>237.67999</v>
@@ -6316,22 +6316,22 @@
         <v>45689</v>
       </c>
       <c r="B155" t="n">
-        <v>240.36157</v>
+        <v>240.36159</v>
       </c>
       <c r="C155" t="n">
-        <v>392.38373</v>
+        <v>392.38376</v>
       </c>
       <c r="D155" t="n">
-        <v>169.28641</v>
+        <v>169.28639</v>
       </c>
       <c r="E155" t="n">
         <v>212.28</v>
       </c>
       <c r="F155" t="n">
-        <v>124.5943</v>
+        <v>124.59429</v>
       </c>
       <c r="G155" t="n">
-        <v>664.38922</v>
+        <v>664.3891599999999</v>
       </c>
       <c r="H155" t="n">
         <v>99.86</v>
@@ -6343,7 +6343,7 @@
         <v>23.73</v>
       </c>
       <c r="K155" t="n">
-        <v>196.5607</v>
+        <v>196.56068</v>
       </c>
       <c r="L155" t="n">
         <v>5954.5</v>
@@ -6357,16 +6357,16 @@
         <v>220.77209</v>
       </c>
       <c r="C156" t="n">
-        <v>371.03439</v>
+        <v>371.03445</v>
       </c>
       <c r="D156" t="n">
-        <v>153.9147</v>
+        <v>153.91472</v>
       </c>
       <c r="E156" t="n">
         <v>190.25999</v>
       </c>
       <c r="F156" t="n">
-        <v>108.10736</v>
+        <v>108.10735</v>
       </c>
       <c r="G156" t="n">
         <v>573.5827</v>
@@ -6381,7 +6381,7 @@
         <v>22.71</v>
       </c>
       <c r="K156" t="n">
-        <v>165.52046</v>
+        <v>165.52045</v>
       </c>
       <c r="L156" t="n">
         <v>5611.8501</v>
@@ -6392,13 +6392,13 @@
         <v>45748</v>
       </c>
       <c r="B157" t="n">
-        <v>211.20094</v>
+        <v>211.20096</v>
       </c>
       <c r="C157" t="n">
-        <v>390.67389</v>
+        <v>390.67383</v>
       </c>
       <c r="D157" t="n">
-        <v>158.05521</v>
+        <v>158.05522</v>
       </c>
       <c r="E157" t="n">
         <v>184.42</v>
@@ -6407,7 +6407,7 @@
         <v>108.646</v>
       </c>
       <c r="G157" t="n">
-        <v>546.35455</v>
+        <v>546.35461</v>
       </c>
       <c r="H157" t="n">
         <v>97.34999999999999</v>
@@ -6430,22 +6430,22 @@
         <v>45778</v>
       </c>
       <c r="B158" t="n">
-        <v>199.88394</v>
+        <v>199.88396</v>
       </c>
       <c r="C158" t="n">
         <v>455.85379</v>
       </c>
       <c r="D158" t="n">
-        <v>170.93452</v>
+        <v>170.93454</v>
       </c>
       <c r="E158" t="n">
         <v>205.00999</v>
       </c>
       <c r="F158" t="n">
-        <v>134.79008</v>
+        <v>134.79007</v>
       </c>
       <c r="G158" t="n">
-        <v>644.37</v>
+        <v>644.37006</v>
       </c>
       <c r="H158" t="n">
         <v>110.73</v>
@@ -6457,7 +6457,7 @@
         <v>19.55</v>
       </c>
       <c r="K158" t="n">
-        <v>239.30917</v>
+        <v>239.30919</v>
       </c>
       <c r="L158" t="n">
         <v>5911.68994</v>
@@ -6474,13 +6474,13 @@
         <v>492.54117</v>
       </c>
       <c r="D159" t="n">
-        <v>175.6158</v>
+        <v>175.61581</v>
       </c>
       <c r="E159" t="n">
         <v>219.39</v>
       </c>
       <c r="F159" t="n">
-        <v>157.60352</v>
+        <v>157.6035</v>
       </c>
       <c r="G159" t="n">
         <v>735.09875</v>
@@ -6518,7 +6518,7 @@
         <v>234.11</v>
       </c>
       <c r="F160" t="n">
-        <v>177.43488</v>
+        <v>177.43486</v>
       </c>
       <c r="G160" t="n">
         <v>770.30542</v>
@@ -6550,7 +6550,7 @@
         <v>502.55511</v>
       </c>
       <c r="D161" t="n">
-        <v>212.16795</v>
+        <v>212.16798</v>
       </c>
       <c r="E161" t="n">
         <v>229</v>
@@ -6559,7 +6559,7 @@
         <v>173.75389</v>
       </c>
       <c r="G161" t="n">
-        <v>735.70624</v>
+        <v>735.70618</v>
       </c>
       <c r="H161" t="n">
         <v>162.63</v>
@@ -6582,13 +6582,13 @@
         <v>45901</v>
       </c>
       <c r="B162" t="n">
-        <v>253.69287</v>
+        <v>253.69289</v>
       </c>
       <c r="C162" t="n">
         <v>513.72327</v>
       </c>
       <c r="D162" t="n">
-        <v>242.46944</v>
+        <v>242.46942</v>
       </c>
       <c r="E162" t="n">
         <v>219.57001</v>
@@ -6597,7 +6597,7 @@
         <v>186.13406</v>
       </c>
       <c r="G162" t="n">
-        <v>731.89734</v>
+        <v>731.8973999999999</v>
       </c>
       <c r="H162" t="n">
         <v>161.78999</v>
@@ -6620,7 +6620,7 @@
         <v>45931</v>
       </c>
       <c r="B163" t="n">
-        <v>269.37491</v>
+        <v>269.37494</v>
       </c>
       <c r="C163" t="n">
         <v>513.58435</v>
@@ -6632,7 +6632,7 @@
         <v>244.22</v>
       </c>
       <c r="F163" t="n">
-        <v>202.00603</v>
+        <v>202.00606</v>
       </c>
       <c r="G163" t="n">
         <v>646.15814</v>
@@ -6647,7 +6647,7 @@
         <v>39.99</v>
       </c>
       <c r="K163" t="n">
-        <v>366.90195</v>
+        <v>366.90198</v>
       </c>
       <c r="L163" t="n">
         <v>6840.2002</v>
@@ -6685,7 +6685,7 @@
         <v>40.56</v>
       </c>
       <c r="K164" t="n">
-        <v>399.98596</v>
+        <v>399.98593</v>
       </c>
       <c r="L164" t="n">
         <v>6849.08984</v>
@@ -6711,7 +6711,7 @@
         <v>186.06461</v>
       </c>
       <c r="G165" t="n">
-        <v>658.39502</v>
+        <v>658.39508</v>
       </c>
       <c r="H165" t="n">
         <v>214.16</v>
@@ -6784,10 +6784,10 @@
         <v>210</v>
       </c>
       <c r="F167" t="n">
-        <v>176.77635</v>
+        <v>176.77634</v>
       </c>
       <c r="G167" t="n">
-        <v>646.51562</v>
+        <v>646.5156899999999</v>
       </c>
       <c r="H167" t="n">
         <v>200.21001</v>
@@ -6822,7 +6822,7 @@
         <v>208.27</v>
       </c>
       <c r="F168" t="n">
-        <v>174.00227</v>
+        <v>174.00226</v>
       </c>
       <c r="G168" t="n">
         <v>571.14948</v>
@@ -6860,7 +6860,7 @@
         <v>265.06</v>
       </c>
       <c r="F169" t="n">
-        <v>199.11488</v>
+        <v>199.11487</v>
       </c>
       <c r="G169" t="n">
         <v>610.86127</v>
@@ -7069,44 +7069,6 @@
       </c>
       <c r="L174" t="n">
         <v>7651.54004</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B175" t="n">
-        <v>342.95999</v>
-      </c>
-      <c r="C175" t="n">
-        <v>533.6900000000001</v>
-      </c>
-      <c r="D175" t="n">
-        <v>347.64001</v>
-      </c>
-      <c r="E175" t="n">
-        <v>254.08</v>
-      </c>
-      <c r="F175" t="n">
-        <v>221.3</v>
-      </c>
-      <c r="G175" t="n">
-        <v>737.53998</v>
-      </c>
-      <c r="H175" t="n">
-        <v>570.82001</v>
-      </c>
-      <c r="I175" t="n">
-        <v>367.16</v>
-      </c>
-      <c r="J175" t="n">
-        <v>98.12</v>
-      </c>
-      <c r="K175" t="n">
-        <v>346.25</v>
-      </c>
-      <c r="L175" t="n">
-        <v>7718.93994</v>
       </c>
     </row>
   </sheetData>
@@ -7182,34 +7144,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00581</v>
+        <v>0.00585</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00178</v>
+        <v>0.00179</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00199</v>
+        <v>0.002</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00236</v>
+        <v>0.00237</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00329</v>
+        <v>0.00331</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00298</v>
+        <v>0.003</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00478</v>
+        <v>0.0048</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00493</v>
+        <v>0.00496</v>
       </c>
       <c r="J2" t="n">
         <v>0.00367</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00258</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="3">
@@ -7219,34 +7181,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00178</v>
+        <v>0.00179</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00425</v>
+        <v>0.00427</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0017</v>
+        <v>0.00171</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00202</v>
+        <v>0.00203</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00281</v>
+        <v>0.00282</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00255</v>
+        <v>0.00256</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00408</v>
+        <v>0.0041</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00421</v>
+        <v>0.00424</v>
       </c>
       <c r="J3" t="n">
         <v>0.00314</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00221</v>
+        <v>0.00222</v>
       </c>
     </row>
     <row r="4">
@@ -7256,34 +7218,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00199</v>
+        <v>0.002</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0017</v>
+        <v>0.00171</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00528</v>
+        <v>0.00531</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00225</v>
+        <v>0.00226</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00313</v>
+        <v>0.00315</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00284</v>
+        <v>0.00286</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00455</v>
+        <v>0.00457</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00469</v>
+        <v>0.00472</v>
       </c>
       <c r="J4" t="n">
         <v>0.0035</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00246</v>
+        <v>0.00247</v>
       </c>
     </row>
     <row r="5">
@@ -7293,34 +7255,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00236</v>
+        <v>0.00237</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00202</v>
+        <v>0.00203</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00225</v>
+        <v>0.00226</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00743</v>
+        <v>0.00748</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00372</v>
+        <v>0.00374</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00337</v>
+        <v>0.00339</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0054</v>
+        <v>0.00543</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00557</v>
+        <v>0.00561</v>
       </c>
       <c r="J5" t="n">
         <v>0.00415</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00292</v>
+        <v>0.00294</v>
       </c>
     </row>
     <row r="6">
@@ -7330,34 +7292,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00329</v>
+        <v>0.00331</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00281</v>
+        <v>0.00282</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00313</v>
+        <v>0.00315</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00372</v>
+        <v>0.00374</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01444</v>
+        <v>0.01449</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0047</v>
+        <v>0.00472</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00753</v>
+        <v>0.00756</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00776</v>
+        <v>0.0078</v>
       </c>
       <c r="J6" t="n">
         <v>0.00578</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00407</v>
+        <v>0.00409</v>
       </c>
     </row>
     <row r="7">
@@ -7367,34 +7329,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00298</v>
+        <v>0.003</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00255</v>
+        <v>0.00256</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00284</v>
+        <v>0.00286</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00337</v>
+        <v>0.00339</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0047</v>
+        <v>0.00472</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01186</v>
+        <v>0.01193</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00682</v>
+        <v>0.00686</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00703</v>
+        <v>0.00708</v>
       </c>
       <c r="J7" t="n">
         <v>0.00524</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00369</v>
+        <v>0.00371</v>
       </c>
     </row>
     <row r="8">
@@ -7404,34 +7366,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00478</v>
+        <v>0.0048</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00408</v>
+        <v>0.0041</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00455</v>
+        <v>0.00457</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0054</v>
+        <v>0.00543</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00753</v>
+        <v>0.00756</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00682</v>
+        <v>0.00686</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03045</v>
+        <v>0.03056</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01127</v>
+        <v>0.01133</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.00839</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00591</v>
+        <v>0.00593</v>
       </c>
     </row>
     <row r="9">
@@ -7441,34 +7403,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00493</v>
+        <v>0.00496</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00421</v>
+        <v>0.00424</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00469</v>
+        <v>0.00472</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00557</v>
+        <v>0.00561</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00776</v>
+        <v>0.0078</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00703</v>
+        <v>0.00708</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01127</v>
+        <v>0.01133</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03239</v>
+        <v>0.03258</v>
       </c>
       <c r="J9" t="n">
         <v>0.008659999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00609</v>
+        <v>0.00613</v>
       </c>
     </row>
     <row r="10">
@@ -7496,13 +7458,13 @@
         <v>0.00524</v>
       </c>
       <c r="H10" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.00839</v>
       </c>
       <c r="I10" t="n">
         <v>0.008659999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01799</v>
+        <v>0.01786</v>
       </c>
       <c r="K10" t="n">
         <v>0.00454</v>
@@ -7515,34 +7477,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.00258</v>
+        <v>0.0026</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00221</v>
+        <v>0.00222</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00246</v>
+        <v>0.00247</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00292</v>
+        <v>0.00294</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00407</v>
+        <v>0.00409</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00369</v>
+        <v>0.00371</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00591</v>
+        <v>0.00593</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00609</v>
+        <v>0.00613</v>
       </c>
       <c r="J11" t="n">
         <v>0.00454</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0089</v>
+        <v>0.00893</v>
       </c>
     </row>
   </sheetData>
@@ -7618,34 +7580,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00581</v>
+        <v>0.00585</v>
       </c>
       <c r="C2" t="n">
+        <v>0.00207</v>
+      </c>
+      <c r="D2" t="n">
         <v>0.00206</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.00205</v>
-      </c>
       <c r="E2" t="n">
-        <v>0.00268</v>
+        <v>0.00269</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00382</v>
+        <v>0.00384</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00258</v>
+        <v>0.0026</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00453</v>
+        <v>0.00456</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00512</v>
+        <v>0.00515</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00318</v>
+        <v>0.00319</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0026</v>
+        <v>0.00262</v>
       </c>
     </row>
     <row r="3">
@@ -7655,34 +7617,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00206</v>
+        <v>0.00207</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00425</v>
+        <v>0.00427</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00192</v>
+        <v>0.00193</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0025</v>
+        <v>0.00251</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00344</v>
+        <v>0.00345</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00232</v>
+        <v>0.00233</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00415</v>
+        <v>0.00418</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00383</v>
+        <v>0.00386</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0025</v>
+        <v>0.00252</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00224</v>
+        <v>0.00226</v>
       </c>
     </row>
     <row r="4">
@@ -7692,34 +7654,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00205</v>
+        <v>0.00206</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00192</v>
+        <v>0.00193</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00528</v>
+        <v>0.00531</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00298</v>
+        <v>0.00299</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00331</v>
+        <v>0.00332</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00272</v>
+        <v>0.00273</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00475</v>
+        <v>0.00477</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00423</v>
+        <v>0.00426</v>
       </c>
       <c r="J4" t="n">
         <v>0.00363</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00275</v>
+        <v>0.00276</v>
       </c>
     </row>
     <row r="5">
@@ -7729,34 +7691,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00268</v>
+        <v>0.00269</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0025</v>
+        <v>0.00251</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00298</v>
+        <v>0.00299</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00743</v>
+        <v>0.00748</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00442</v>
+        <v>0.00443</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00347</v>
+        <v>0.00349</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00615</v>
+        <v>0.00618</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00535</v>
+        <v>0.00539</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00353</v>
+        <v>0.00354</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00305</v>
+        <v>0.00306</v>
       </c>
     </row>
     <row r="6">
@@ -7766,34 +7728,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00382</v>
+        <v>0.00384</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00344</v>
+        <v>0.00345</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00331</v>
+        <v>0.00332</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00442</v>
+        <v>0.00443</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01444</v>
+        <v>0.01449</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00457</v>
+        <v>0.00459</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00893</v>
+        <v>0.00894</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00721</v>
+        <v>0.00725</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00495</v>
+        <v>0.00493</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00437</v>
+        <v>0.00438</v>
       </c>
     </row>
     <row r="7">
@@ -7803,34 +7765,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00258</v>
+        <v>0.0026</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00232</v>
+        <v>0.00233</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00272</v>
+        <v>0.00273</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00347</v>
+        <v>0.00349</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00457</v>
+        <v>0.00459</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01186</v>
+        <v>0.01193</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00601</v>
+        <v>0.00605</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0062</v>
+        <v>0.00625</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00369</v>
+        <v>0.0037</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00331</v>
+        <v>0.00333</v>
       </c>
     </row>
     <row r="8">
@@ -7840,34 +7802,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00453</v>
+        <v>0.00456</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00415</v>
+        <v>0.00418</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00475</v>
+        <v>0.00477</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00615</v>
+        <v>0.00618</v>
       </c>
       <c r="F8" t="n">
+        <v>0.00894</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.00605</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.03056</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.009809999999999999</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.00893</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.00601</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.03045</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.00974</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.008970000000000001</v>
-      </c>
       <c r="K8" t="n">
-        <v>0.00602</v>
+        <v>0.00603</v>
       </c>
     </row>
     <row r="9">
@@ -7877,34 +7839,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00512</v>
+        <v>0.00515</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00383</v>
+        <v>0.00386</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00423</v>
+        <v>0.00426</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00535</v>
+        <v>0.00539</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00721</v>
+        <v>0.00725</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0062</v>
+        <v>0.00625</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00974</v>
+        <v>0.009809999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03239</v>
+        <v>0.03258</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00621</v>
+        <v>0.00623</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00561</v>
+        <v>0.00564</v>
       </c>
     </row>
     <row r="10">
@@ -7914,34 +7876,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00318</v>
+        <v>0.00319</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0025</v>
+        <v>0.00252</v>
       </c>
       <c r="D10" t="n">
         <v>0.00363</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00353</v>
+        <v>0.00354</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00495</v>
+        <v>0.00493</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00369</v>
+        <v>0.0037</v>
       </c>
       <c r="H10" t="n">
-        <v>0.008970000000000001</v>
+        <v>0.00893</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00621</v>
+        <v>0.00623</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01799</v>
+        <v>0.01786</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00421</v>
+        <v>0.0042</v>
       </c>
     </row>
     <row r="11">
@@ -7951,34 +7913,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0026</v>
+        <v>0.00262</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00224</v>
+        <v>0.00226</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00275</v>
+        <v>0.00276</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00305</v>
+        <v>0.00306</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00437</v>
+        <v>0.00438</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00331</v>
+        <v>0.00333</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00602</v>
+        <v>0.00603</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00561</v>
+        <v>0.00564</v>
       </c>
       <c r="J11" t="n">
-        <v>0.00421</v>
+        <v>0.0042</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0089</v>
+        <v>0.00893</v>
       </c>
     </row>
   </sheetData>
@@ -8054,34 +8016,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00581</v>
+        <v>0.00585</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00184</v>
+        <v>0.00185</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00207</v>
+        <v>0.00208</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00252</v>
+        <v>0.00254</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00322</v>
+        <v>0.00324</v>
       </c>
       <c r="G2" t="n">
+        <v>0.00221</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.00425</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.00337</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.00257</v>
+      </c>
+      <c r="K2" t="n">
         <v>0.0022</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.00422</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.00335</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.00256</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.00219</v>
       </c>
     </row>
     <row r="3">
@@ -8091,34 +8053,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00184</v>
+        <v>0.00185</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00425</v>
+        <v>0.00427</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00174</v>
+        <v>0.00175</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00212</v>
+        <v>0.00213</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0027</v>
+        <v>0.00271</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00184</v>
+        <v>0.00185</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00354</v>
+        <v>0.00356</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00281</v>
+        <v>0.00283</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00214</v>
+        <v>0.00215</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00184</v>
+        <v>0.00185</v>
       </c>
     </row>
     <row r="4">
@@ -8128,34 +8090,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00207</v>
+        <v>0.00208</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00174</v>
+        <v>0.00175</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00528</v>
+        <v>0.00531</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00239</v>
+        <v>0.0024</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00305</v>
+        <v>0.00306</v>
       </c>
       <c r="G4" t="n">
+        <v>0.00209</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.00402</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.00319</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.00243</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.00208</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.00317</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.00242</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.00207</v>
       </c>
     </row>
     <row r="5">
@@ -8165,34 +8127,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00252</v>
+        <v>0.00254</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00212</v>
+        <v>0.00213</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00239</v>
+        <v>0.0024</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00743</v>
+        <v>0.00748</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00371</v>
+        <v>0.00373</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00253</v>
+        <v>0.00255</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00487</v>
+        <v>0.0049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00386</v>
+        <v>0.00389</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00295</v>
+        <v>0.00296</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00252</v>
+        <v>0.00254</v>
       </c>
     </row>
     <row r="6">
@@ -8202,34 +8164,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00322</v>
+        <v>0.00324</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0027</v>
+        <v>0.00271</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00305</v>
+        <v>0.00306</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00371</v>
+        <v>0.00373</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01444</v>
+        <v>0.01449</v>
       </c>
       <c r="G6" t="n">
+        <v>0.00325</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.00624</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.00496</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.00377</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.00323</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.00621</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.00493</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.00376</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.00322</v>
       </c>
     </row>
     <row r="7">
@@ -8239,34 +8201,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0022</v>
+        <v>0.00221</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00184</v>
+        <v>0.00185</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00208</v>
+        <v>0.00209</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00253</v>
+        <v>0.00255</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00323</v>
+        <v>0.00325</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01186</v>
+        <v>0.01193</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00424</v>
+        <v>0.00426</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00336</v>
+        <v>0.00338</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00257</v>
+        <v>0.00258</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0022</v>
+        <v>0.00221</v>
       </c>
     </row>
     <row r="8">
@@ -8276,34 +8238,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00422</v>
+        <v>0.00425</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00354</v>
+        <v>0.00356</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004</v>
+        <v>0.00402</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00487</v>
+        <v>0.0049</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00621</v>
+        <v>0.00624</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00424</v>
+        <v>0.00426</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03045</v>
+        <v>0.03056</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00647</v>
+        <v>0.00651</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00493</v>
+        <v>0.00495</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00423</v>
+        <v>0.00425</v>
       </c>
     </row>
     <row r="9">
@@ -8313,34 +8275,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00335</v>
+        <v>0.00337</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00281</v>
+        <v>0.00283</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00317</v>
+        <v>0.00319</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00386</v>
+        <v>0.00389</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00493</v>
+        <v>0.00496</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00336</v>
+        <v>0.00338</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00647</v>
+        <v>0.00651</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03239</v>
+        <v>0.03258</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00391</v>
+        <v>0.00393</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00335</v>
+        <v>0.00337</v>
       </c>
     </row>
     <row r="10">
@@ -8350,34 +8312,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00256</v>
+        <v>0.00257</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00214</v>
+        <v>0.00215</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00242</v>
+        <v>0.00243</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00295</v>
+        <v>0.00296</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00376</v>
+        <v>0.00377</v>
       </c>
       <c r="G10" t="n">
+        <v>0.00258</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.00495</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.00393</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="K10" t="n">
         <v>0.00257</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.00493</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.00391</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.01799</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.00256</v>
       </c>
     </row>
     <row r="11">
@@ -8387,34 +8349,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.00219</v>
+        <v>0.0022</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00184</v>
+        <v>0.00185</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00207</v>
+        <v>0.00208</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00252</v>
+        <v>0.00254</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00322</v>
+        <v>0.00323</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0022</v>
+        <v>0.00221</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00423</v>
+        <v>0.00425</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00335</v>
+        <v>0.00337</v>
       </c>
       <c r="J11" t="n">
-        <v>0.00256</v>
+        <v>0.00257</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0089</v>
+        <v>0.00893</v>
       </c>
     </row>
   </sheetData>
@@ -8490,34 +8452,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00581</v>
+        <v>0.00585</v>
       </c>
       <c r="C2" t="n">
+        <v>0.00212</v>
+      </c>
+      <c r="D2" t="n">
         <v>0.00211</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.00209</v>
-      </c>
       <c r="E2" t="n">
-        <v>0.00279</v>
+        <v>0.0028</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00384</v>
+        <v>0.00385</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00214</v>
+        <v>0.00215</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00423</v>
+        <v>0.00426</v>
       </c>
       <c r="I2" t="n">
         <v>0.00434</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00256</v>
+        <v>0.00258</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0024</v>
+        <v>0.00241</v>
       </c>
     </row>
     <row r="3">
@@ -8527,34 +8489,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00211</v>
+        <v>0.00212</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00425</v>
+        <v>0.00427</v>
       </c>
       <c r="D3" t="n">
+        <v>0.00197</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.00345</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.00195</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="J3" t="n">
         <v>0.00196</v>
       </c>
-      <c r="E3" t="n">
-        <v>0.00259</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.00344</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.00194</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.00388</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.00308</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.00193</v>
-      </c>
       <c r="K3" t="n">
-        <v>0.00206</v>
+        <v>0.00207</v>
       </c>
     </row>
     <row r="4">
@@ -8564,28 +8526,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00209</v>
+        <v>0.00211</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00196</v>
+        <v>0.00197</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00528</v>
+        <v>0.00531</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00312</v>
+        <v>0.00313</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00328</v>
+        <v>0.00329</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00232</v>
+        <v>0.00233</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00448</v>
+        <v>0.0045</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00342</v>
+        <v>0.00343</v>
       </c>
       <c r="J4" t="n">
         <v>0.00309</v>
@@ -8601,34 +8563,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00279</v>
+        <v>0.0028</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00259</v>
+        <v>0.0026</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00312</v>
+        <v>0.00313</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00743</v>
+        <v>0.00748</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00448</v>
+        <v>0.00449</v>
       </c>
       <c r="G5" t="n">
         <v>0.00306</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00595</v>
+        <v>0.00597</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00446</v>
+        <v>0.00448</v>
       </c>
       <c r="J5" t="n">
+        <v>0.00288</v>
+      </c>
+      <c r="K5" t="n">
         <v>0.00286</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.00285</v>
       </c>
     </row>
     <row r="6">
@@ -8638,31 +8600,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00384</v>
+        <v>0.00385</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00344</v>
+        <v>0.00345</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00328</v>
+        <v>0.00329</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00448</v>
+        <v>0.00449</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01444</v>
+        <v>0.01449</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0038</v>
+        <v>0.00381</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00838</v>
+        <v>0.008359999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00571</v>
+        <v>0.00573</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00384</v>
+        <v>0.00382</v>
       </c>
       <c r="K6" t="n">
         <v>0.00396</v>
@@ -8675,34 +8637,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00214</v>
+        <v>0.00215</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00194</v>
+        <v>0.00195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00232</v>
+        <v>0.00233</v>
       </c>
       <c r="E7" t="n">
         <v>0.00306</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0038</v>
+        <v>0.00381</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01186</v>
+        <v>0.01193</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00462</v>
+        <v>0.00464</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00425</v>
+        <v>0.00426</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00218</v>
+        <v>0.00219</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00251</v>
+        <v>0.00252</v>
       </c>
     </row>
     <row r="8">
@@ -8712,34 +8674,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00423</v>
+        <v>0.00426</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00388</v>
+        <v>0.0039</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00448</v>
+        <v>0.0045</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00595</v>
+        <v>0.00597</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00838</v>
+        <v>0.008359999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00462</v>
+        <v>0.00464</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03045</v>
+        <v>0.03056</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00715</v>
+        <v>0.00718</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00725</v>
+        <v>0.00718</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00517</v>
+        <v>0.00516</v>
       </c>
     </row>
     <row r="9">
@@ -8752,31 +8714,31 @@
         <v>0.00434</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00308</v>
+        <v>0.0031</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00342</v>
+        <v>0.00343</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00446</v>
+        <v>0.00448</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00571</v>
+        <v>0.00573</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00425</v>
+        <v>0.00426</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00715</v>
+        <v>0.00718</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03239</v>
+        <v>0.03258</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00356</v>
+        <v>0.00358</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00416</v>
+        <v>0.00417</v>
       </c>
     </row>
     <row r="10">
@@ -8786,34 +8748,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00256</v>
+        <v>0.00258</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00193</v>
+        <v>0.00196</v>
       </c>
       <c r="D10" t="n">
         <v>0.00309</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00286</v>
+        <v>0.00288</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00384</v>
+        <v>0.00382</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00218</v>
+        <v>0.00219</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00725</v>
+        <v>0.00718</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00356</v>
+        <v>0.00358</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01799</v>
+        <v>0.01786</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00317</v>
+        <v>0.00315</v>
       </c>
     </row>
     <row r="11">
@@ -8823,34 +8785,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0024</v>
+        <v>0.00241</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00206</v>
+        <v>0.00207</v>
       </c>
       <c r="D11" t="n">
         <v>0.00258</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00285</v>
+        <v>0.00286</v>
       </c>
       <c r="F11" t="n">
         <v>0.00396</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00251</v>
+        <v>0.00252</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00517</v>
+        <v>0.00516</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00416</v>
+        <v>0.00417</v>
       </c>
       <c r="J11" t="n">
-        <v>0.00317</v>
+        <v>0.00315</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0089</v>
+        <v>0.00893</v>
       </c>
     </row>
   </sheetData>
@@ -8926,34 +8888,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0062</v>
+        <v>0.00623</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00237</v>
+        <v>0.00238</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00207</v>
+        <v>0.00208</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00302</v>
+        <v>0.00304</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00437</v>
+        <v>0.0044</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00198</v>
+        <v>0.00199</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00419</v>
+        <v>0.00422</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00527</v>
+        <v>0.0053</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00253</v>
+        <v>0.00255</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00254</v>
+        <v>0.00256</v>
       </c>
     </row>
     <row r="3">
@@ -8963,34 +8925,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00237</v>
+        <v>0.00238</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0046</v>
+        <v>0.00463</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00216</v>
+        <v>0.00217</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00306</v>
+        <v>0.00307</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00409</v>
+        <v>0.00412</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00193</v>
+        <v>0.00194</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00416</v>
+        <v>0.0042</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00333</v>
+        <v>0.00335</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00172</v>
+        <v>0.00175</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00221</v>
+        <v>0.00223</v>
       </c>
     </row>
     <row r="4">
@@ -9000,34 +8962,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00207</v>
+        <v>0.00208</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00216</v>
+        <v>0.00217</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00566</v>
+        <v>0.00569</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00387</v>
+        <v>0.00389</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00341</v>
+        <v>0.00342</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00247</v>
+        <v>0.00249</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00493</v>
+        <v>0.00495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00362</v>
+        <v>0.00364</v>
       </c>
       <c r="J4" t="n">
         <v>0.00369</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00301</v>
+        <v>0.00302</v>
       </c>
     </row>
     <row r="5">
@@ -9037,34 +8999,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00302</v>
+        <v>0.00304</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00306</v>
+        <v>0.00307</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00387</v>
+        <v>0.00389</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007820000000000001</v>
+        <v>0.00787</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00508</v>
+        <v>0.00511</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00345</v>
+        <v>0.00347</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00697</v>
+        <v>0.00701</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00502</v>
+        <v>0.00505</v>
       </c>
       <c r="J5" t="n">
         <v>0.00277</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00306</v>
+        <v>0.00308</v>
       </c>
     </row>
     <row r="6">
@@ -9074,31 +9036,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00437</v>
+        <v>0.0044</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00409</v>
+        <v>0.00412</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00341</v>
+        <v>0.00342</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00508</v>
+        <v>0.00511</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01463</v>
+        <v>0.01468</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00419</v>
+        <v>0.00421</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01044</v>
+        <v>0.01046</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00648</v>
+        <v>0.00652</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00398</v>
+        <v>0.00391</v>
       </c>
       <c r="K6" t="n">
         <v>0.00464</v>
@@ -9111,34 +9073,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00198</v>
+        <v>0.00199</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00193</v>
+        <v>0.00194</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00247</v>
+        <v>0.00249</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00345</v>
+        <v>0.00347</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00419</v>
+        <v>0.00421</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0121</v>
+        <v>0.01218</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00501</v>
+        <v>0.00504</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00514</v>
+        <v>0.00517</v>
       </c>
       <c r="J7" t="n">
         <v>0.00185</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00274</v>
+        <v>0.00275</v>
       </c>
     </row>
     <row r="8">
@@ -9148,34 +9110,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00419</v>
+        <v>0.00422</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00416</v>
+        <v>0.0042</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00493</v>
+        <v>0.00495</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00697</v>
+        <v>0.00701</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01044</v>
+        <v>0.01046</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00501</v>
+        <v>0.00504</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03018</v>
+        <v>0.03028</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00777</v>
+        <v>0.00781</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009560000000000001</v>
+        <v>0.009480000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00608</v>
+        <v>0.00609</v>
       </c>
     </row>
     <row r="9">
@@ -9185,34 +9147,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00527</v>
+        <v>0.0053</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00333</v>
+        <v>0.00335</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00362</v>
+        <v>0.00364</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00502</v>
+        <v>0.00505</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00648</v>
+        <v>0.00652</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00514</v>
+        <v>0.00517</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00777</v>
+        <v>0.00781</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03206</v>
+        <v>0.03225</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00312</v>
+        <v>0.00313</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00494</v>
+        <v>0.00496</v>
       </c>
     </row>
     <row r="10">
@@ -9222,10 +9184,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00253</v>
+        <v>0.00255</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00172</v>
+        <v>0.00175</v>
       </c>
       <c r="D10" t="n">
         <v>0.00369</v>
@@ -9234,22 +9196,22 @@
         <v>0.00277</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00398</v>
+        <v>0.00391</v>
       </c>
       <c r="G10" t="n">
         <v>0.00185</v>
       </c>
       <c r="H10" t="n">
-        <v>0.009560000000000001</v>
+        <v>0.009480000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00312</v>
+        <v>0.00313</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01774</v>
+        <v>0.01762</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00371</v>
+        <v>0.00368</v>
       </c>
     </row>
     <row r="11">
@@ -9259,34 +9221,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.00254</v>
+        <v>0.00256</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00221</v>
+        <v>0.00223</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00301</v>
+        <v>0.00302</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00306</v>
+        <v>0.00308</v>
       </c>
       <c r="F11" t="n">
         <v>0.00464</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00274</v>
+        <v>0.00275</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00608</v>
+        <v>0.00609</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00494</v>
+        <v>0.00496</v>
       </c>
       <c r="J11" t="n">
-        <v>0.00371</v>
+        <v>0.00368</v>
       </c>
       <c r="K11" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.009339999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -9342,22 +9304,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.20331</v>
+        <v>0.20324</v>
       </c>
       <c r="C2" t="n">
-        <v>0.21056</v>
+        <v>0.21034</v>
       </c>
       <c r="D2" t="n">
-        <v>0.20544</v>
+        <v>0.20533</v>
       </c>
       <c r="E2" t="n">
-        <v>0.21158</v>
+        <v>0.21147</v>
       </c>
       <c r="F2" t="n">
-        <v>0.19451</v>
+        <v>0.19396</v>
       </c>
       <c r="G2" t="n">
-        <v>0.20529</v>
+        <v>0.20522</v>
       </c>
     </row>
     <row r="3">
@@ -9367,22 +9329,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.39379</v>
+        <v>0.39368</v>
       </c>
       <c r="C3" t="n">
-        <v>0.32508</v>
+        <v>0.32474</v>
       </c>
       <c r="D3" t="n">
-        <v>0.37846</v>
+        <v>0.37826</v>
       </c>
       <c r="E3" t="n">
-        <v>0.39522</v>
+        <v>0.39536</v>
       </c>
       <c r="F3" t="n">
-        <v>0.38048</v>
+        <v>0.37991</v>
       </c>
       <c r="G3" t="n">
-        <v>0.36896</v>
+        <v>0.36852</v>
       </c>
     </row>
     <row r="4">
@@ -9392,22 +9354,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.23014</v>
+        <v>0.23006</v>
       </c>
       <c r="C4" t="n">
-        <v>0.21526</v>
+        <v>0.21504</v>
       </c>
       <c r="D4" t="n">
-        <v>0.22832</v>
+        <v>0.22818</v>
       </c>
       <c r="E4" t="n">
-        <v>0.25578</v>
+        <v>0.25563</v>
       </c>
       <c r="F4" t="n">
-        <v>0.23139</v>
+        <v>0.23092</v>
       </c>
       <c r="G4" t="n">
-        <v>0.22355</v>
+        <v>0.22344</v>
       </c>
     </row>
     <row r="5">
@@ -9420,16 +9382,16 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01384</v>
+        <v>0.01388</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03994</v>
+        <v>0.04053</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01151</v>
+        <v>0.01271</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -9467,22 +9429,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08304</v>
+        <v>0.08305</v>
       </c>
       <c r="C7" t="n">
-        <v>0.10099</v>
+        <v>0.101</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08527999999999999</v>
+        <v>0.0853</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03623</v>
+        <v>0.03576</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07482</v>
+        <v>0.07456</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09365999999999999</v>
+        <v>0.09375</v>
       </c>
     </row>
     <row r="8">
@@ -9542,22 +9504,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03243</v>
+        <v>0.03262</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04717</v>
+        <v>0.04771</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03534</v>
+        <v>0.03565</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02611</v>
+        <v>0.02637</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03686</v>
+        <v>0.03732</v>
       </c>
     </row>
     <row r="11">
@@ -9567,22 +9529,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05729</v>
+        <v>0.05736</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0871</v>
+        <v>0.08727</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06716</v>
+        <v>0.06729</v>
       </c>
       <c r="E11" t="n">
         <v>0.06125</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08119</v>
+        <v>0.08157</v>
       </c>
       <c r="G11" t="n">
-        <v>0.07169</v>
+        <v>0.07174999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -9613,7 +9575,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05495</v>
+        <v>0.05511</v>
       </c>
     </row>
     <row r="3">
@@ -9623,7 +9585,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05521</v>
+        <v>0.05536</v>
       </c>
     </row>
     <row r="4">
@@ -9633,7 +9595,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05349</v>
+        <v>0.05364</v>
       </c>
     </row>
     <row r="5">
@@ -9643,7 +9605,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0541</v>
+        <v>0.05424</v>
       </c>
     </row>
     <row r="6">
@@ -9653,7 +9615,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05359</v>
+        <v>0.05372</v>
       </c>
     </row>
     <row r="7">
@@ -9663,7 +9625,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05541</v>
+        <v>0.05557</v>
       </c>
     </row>
   </sheetData>
@@ -9677,7 +9639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K174"/>
+  <dimension ref="A1:K173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9941,7 +9903,7 @@
         <v>0.20228</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.08592</v>
+        <v>-0.08591</v>
       </c>
       <c r="K7" t="n">
         <v>0.06267</v>
@@ -9990,7 +9952,7 @@
         <v>-0.14409</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0277</v>
+        <v>0.02771</v>
       </c>
       <c r="D9" t="n">
         <v>0.06829</v>
@@ -10119,7 +10081,7 @@
         <v>0.09661</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.11024</v>
+        <v>-0.11025</v>
       </c>
     </row>
     <row r="13">
@@ -10197,7 +10159,7 @@
         <v>41456</v>
       </c>
       <c r="B15" t="n">
-        <v>0.14122</v>
+        <v>0.14123</v>
       </c>
       <c r="C15" t="n">
         <v>-0.07817</v>
@@ -10238,7 +10200,7 @@
         <v>0.05639</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.04601</v>
+        <v>-0.04602</v>
       </c>
       <c r="E16" t="n">
         <v>-0.06719</v>
@@ -10629,7 +10591,7 @@
         <v>-0.0363</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0561</v>
+        <v>-0.05609</v>
       </c>
       <c r="G27" t="n">
         <v>0.07965999999999999</v>
@@ -10664,7 +10626,7 @@
         <v>0.08323</v>
       </c>
       <c r="F28" t="n">
-        <v>0.11634</v>
+        <v>0.11635</v>
       </c>
       <c r="G28" t="n">
         <v>0.02987</v>
@@ -10769,7 +10731,7 @@
         <v>0.10862</v>
       </c>
       <c r="F31" t="n">
-        <v>0.07772999999999999</v>
+        <v>0.07772</v>
       </c>
       <c r="G31" t="n">
         <v>0.03614</v>
@@ -10994,7 +10956,7 @@
         <v>0.06633</v>
       </c>
       <c r="K37" t="n">
-        <v>0.26685</v>
+        <v>0.26686</v>
       </c>
     </row>
     <row r="38">
@@ -11274,7 +11236,7 @@
         <v>-0.09956</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.07881000000000001</v>
+        <v>-0.07882</v>
       </c>
     </row>
     <row r="46">
@@ -11481,7 +11443,7 @@
         <v>0.10604</v>
       </c>
       <c r="J51" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.06281</v>
       </c>
       <c r="K51" t="n">
         <v>0.04234</v>
@@ -11551,7 +11513,7 @@
         <v>-0.03764</v>
       </c>
       <c r="J53" t="n">
-        <v>0.05183</v>
+        <v>0.05182</v>
       </c>
       <c r="K53" t="n">
         <v>-0.01916</v>
@@ -11656,7 +11618,7 @@
         <v>0.12825</v>
       </c>
       <c r="J56" t="n">
-        <v>0.04525</v>
+        <v>0.04524</v>
       </c>
       <c r="K56" t="n">
         <v>0.04276</v>
@@ -11936,7 +11898,7 @@
         <v>0.10026</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.00385</v>
+        <v>-0.00386</v>
       </c>
       <c r="K64" t="n">
         <v>0.02193</v>
@@ -12122,7 +12084,7 @@
         <v>43132</v>
       </c>
       <c r="B70" t="n">
-        <v>0.06819</v>
+        <v>0.06818</v>
       </c>
       <c r="C70" t="n">
         <v>-0.00842</v>
@@ -12487,7 +12449,7 @@
         <v>-0.18314</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.0677</v>
+        <v>-0.06771000000000001</v>
       </c>
       <c r="H80" t="n">
         <v>-0.13333</v>
@@ -12954,7 +12916,7 @@
         <v>0.06816999999999999</v>
       </c>
       <c r="K93" t="n">
-        <v>-0.03437</v>
+        <v>-0.03436</v>
       </c>
     </row>
     <row r="94">
@@ -13248,7 +13210,7 @@
         <v>-0.03737</v>
       </c>
       <c r="D102" t="n">
-        <v>0.1027</v>
+        <v>0.10269</v>
       </c>
       <c r="E102" t="n">
         <v>-0.03575</v>
@@ -13388,7 +13350,7 @@
         <v>0.00412</v>
       </c>
       <c r="D106" t="n">
-        <v>0.10646</v>
+        <v>0.10647</v>
       </c>
       <c r="E106" t="n">
         <v>-0.03533</v>
@@ -13689,7 +13651,7 @@
         <v>-0.08033</v>
       </c>
       <c r="K114" t="n">
-        <v>0.09637999999999999</v>
+        <v>0.09639</v>
       </c>
     </row>
     <row r="115">
@@ -13770,7 +13732,7 @@
         <v>-0.01571</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.07535</v>
+        <v>-0.07534</v>
       </c>
       <c r="D117" t="n">
         <v>-0.06592000000000001</v>
@@ -13843,7 +13805,7 @@
         <v>0.03186</v>
       </c>
       <c r="D119" t="n">
-        <v>0.02969</v>
+        <v>0.0297</v>
       </c>
       <c r="E119" t="n">
         <v>0.06144</v>
@@ -14389,7 +14351,7 @@
         <v>0.06361</v>
       </c>
       <c r="K134" t="n">
-        <v>0.07932</v>
+        <v>0.07933</v>
       </c>
     </row>
     <row r="135">
@@ -15755,41 +15717,6 @@
       </c>
       <c r="K173" t="n">
         <v>-0.04998</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B174" t="n">
-        <v>0.02985</v>
-      </c>
-      <c r="C174" t="n">
-        <v>0.04053</v>
-      </c>
-      <c r="D174" t="n">
-        <v>0.01035</v>
-      </c>
-      <c r="E174" t="n">
-        <v>0.01979</v>
-      </c>
-      <c r="F174" t="n">
-        <v>-0.031</v>
-      </c>
-      <c r="G174" t="n">
-        <v>0.01704</v>
-      </c>
-      <c r="H174" t="n">
-        <v>-0.06691999999999999</v>
-      </c>
-      <c r="I174" t="n">
-        <v>0.03481</v>
-      </c>
-      <c r="J174" t="n">
-        <v>-0.1839</v>
-      </c>
-      <c r="K174" t="n">
-        <v>-0.01407</v>
       </c>
     </row>
   </sheetData>
@@ -15850,10 +15777,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0203</v>
+        <v>0.0202</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0765</v>
+        <v>0.0767</v>
       </c>
       <c r="D2" t="n">
         <v>-0.1812</v>
@@ -15862,10 +15789,10 @@
         <v>0.2166</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.0956</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.3939</v>
+        <v>-0.409</v>
       </c>
     </row>
     <row r="3">
@@ -15875,10 +15802,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0204</v>
+        <v>0.0203</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0654</v>
+        <v>0.0655</v>
       </c>
       <c r="D3" t="n">
         <v>-0.1715</v>
@@ -15887,10 +15814,10 @@
         <v>0.2458</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2438</v>
+        <v>0.2486</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7331</v>
+        <v>0.7175</v>
       </c>
     </row>
     <row r="4">
@@ -15900,10 +15827,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0211</v>
+        <v>0.0212</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0731</v>
       </c>
       <c r="D4" t="n">
         <v>-0.1795</v>
@@ -15912,10 +15839,10 @@
         <v>0.3382</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4054</v>
+        <v>0.4017</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6465</v>
+        <v>1.6196</v>
       </c>
     </row>
     <row r="5">
@@ -15928,7 +15855,7 @@
         <v>0.0221</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.0867</v>
       </c>
       <c r="D5" t="n">
         <v>-0.2375</v>
@@ -15937,10 +15864,10 @@
         <v>0.2727</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3177</v>
+        <v>0.3164</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7637</v>
+        <v>0.7418</v>
       </c>
     </row>
     <row r="6">
@@ -15950,10 +15877,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0462</v>
+        <v>0.0467</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1205</v>
+        <v>0.1207</v>
       </c>
       <c r="D6" t="n">
         <v>-0.3203</v>
@@ -15962,10 +15889,10 @@
         <v>0.3854</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1072</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5938</v>
+        <v>0.5879</v>
       </c>
     </row>
     <row r="7">
@@ -15975,10 +15902,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0246</v>
+        <v>0.0247</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1092</v>
+        <v>0.1095</v>
       </c>
       <c r="D7" t="n">
         <v>-0.3263</v>
@@ -15987,10 +15914,10 @@
         <v>0.4791</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2679</v>
+        <v>0.2659</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3474</v>
+        <v>2.3167</v>
       </c>
     </row>
     <row r="8">
@@ -16000,10 +15927,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0408</v>
+        <v>0.0414</v>
       </c>
       <c r="C8" t="n">
-        <v>0.175</v>
+        <v>0.1753</v>
       </c>
       <c r="D8" t="n">
         <v>-0.4105</v>
@@ -16012,10 +15939,10 @@
         <v>0.7426</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2872</v>
+        <v>1.2709</v>
       </c>
     </row>
     <row r="9">
@@ -16028,7 +15955,7 @@
         <v>0.0451</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1805</v>
+        <v>0.181</v>
       </c>
       <c r="D9" t="n">
         <v>-0.3673</v>
@@ -16037,10 +15964,10 @@
         <v>0.8107</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1035</v>
+        <v>1.0994</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4411</v>
+        <v>2.4087</v>
       </c>
     </row>
     <row r="10">
@@ -16050,10 +15977,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0173</v>
+        <v>0.0185</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1345</v>
+        <v>0.134</v>
       </c>
       <c r="D10" t="n">
         <v>-0.354</v>
@@ -16062,10 +15989,10 @@
         <v>1.1409</v>
       </c>
       <c r="F10" t="n">
-        <v>3.406</v>
+        <v>3.4576</v>
       </c>
       <c r="G10" t="n">
-        <v>28.168</v>
+        <v>28.6664</v>
       </c>
     </row>
     <row r="11">
@@ -16075,10 +16002,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0334</v>
+        <v>0.0337</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0946</v>
+        <v>0.0948</v>
       </c>
       <c r="D11" t="n">
         <v>-0.2097</v>
@@ -16087,10 +16014,10 @@
         <v>0.4342</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7534</v>
+        <v>0.7448</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0708</v>
+        <v>2.0475</v>
       </c>
     </row>
   </sheetData>
@@ -16166,34 +16093,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00581</v>
+        <v>0.00585</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0024</v>
+        <v>0.00241</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00212</v>
+        <v>0.00213</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00307</v>
+        <v>0.00309</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00448</v>
+        <v>0.00451</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00208</v>
+        <v>0.0021</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00424</v>
+        <v>0.00427</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00537</v>
+        <v>0.0054</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00257</v>
+        <v>0.0026</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00263</v>
+        <v>0.00264</v>
       </c>
     </row>
     <row r="3">
@@ -16203,34 +16130,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0024</v>
+        <v>0.00241</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00425</v>
+        <v>0.00427</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00219</v>
+        <v>0.0022</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00309</v>
+        <v>0.00311</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00421</v>
+        <v>0.00424</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00203</v>
+        <v>0.00205</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00423</v>
+        <v>0.00427</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00337</v>
+        <v>0.00339</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00172</v>
+        <v>0.00175</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00229</v>
+        <v>0.00231</v>
       </c>
     </row>
     <row r="4">
@@ -16240,34 +16167,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00212</v>
+        <v>0.00213</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00219</v>
+        <v>0.0022</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00528</v>
+        <v>0.00531</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00389</v>
+        <v>0.00391</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00353</v>
+        <v>0.00354</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00256</v>
+        <v>0.00258</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00499</v>
+        <v>0.00501</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00367</v>
+        <v>0.00369</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00379</v>
+        <v>0.0038</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00311</v>
+        <v>0.00312</v>
       </c>
     </row>
     <row r="5">
@@ -16277,34 +16204,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00307</v>
+        <v>0.00309</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00309</v>
+        <v>0.00311</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00389</v>
+        <v>0.00391</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00743</v>
+        <v>0.00748</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00528</v>
+        <v>0.00531</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0036</v>
+        <v>0.00362</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00708</v>
+        <v>0.00712</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00508</v>
+        <v>0.00511</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00277</v>
+        <v>0.00279</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0032</v>
+        <v>0.00322</v>
       </c>
     </row>
     <row r="6">
@@ -16314,31 +16241,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00448</v>
+        <v>0.00451</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00421</v>
+        <v>0.00424</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00353</v>
+        <v>0.00354</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00528</v>
+        <v>0.00531</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01444</v>
+        <v>0.01449</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00441</v>
+        <v>0.00443</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01065</v>
+        <v>0.01066</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00653</v>
+        <v>0.00656</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00393</v>
+        <v>0.00386</v>
       </c>
       <c r="K6" t="n">
         <v>0.00474</v>
@@ -16351,34 +16278,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00208</v>
+        <v>0.0021</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00203</v>
+        <v>0.00205</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00256</v>
+        <v>0.00258</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0036</v>
+        <v>0.00362</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00441</v>
+        <v>0.00443</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01186</v>
+        <v>0.01193</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00502</v>
+        <v>0.00505</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00518</v>
+        <v>0.00521</v>
       </c>
       <c r="J7" t="n">
         <v>0.00178</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00284</v>
+        <v>0.00285</v>
       </c>
     </row>
     <row r="8">
@@ -16388,34 +16315,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00424</v>
+        <v>0.00427</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00423</v>
+        <v>0.00427</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00499</v>
+        <v>0.00501</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00708</v>
+        <v>0.00712</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01065</v>
+        <v>0.01066</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00502</v>
+        <v>0.00505</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03045</v>
+        <v>0.03056</v>
       </c>
       <c r="I8" t="n">
-        <v>0.007860000000000001</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00967</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00615</v>
+        <v>0.00616</v>
       </c>
     </row>
     <row r="9">
@@ -16425,34 +16352,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00537</v>
+        <v>0.0054</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00337</v>
+        <v>0.00339</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00367</v>
+        <v>0.00369</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00508</v>
+        <v>0.00511</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00653</v>
+        <v>0.00656</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00518</v>
+        <v>0.00521</v>
       </c>
       <c r="H9" t="n">
-        <v>0.007860000000000001</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03239</v>
+        <v>0.03258</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00319</v>
+        <v>0.0032</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00501</v>
+        <v>0.00504</v>
       </c>
     </row>
     <row r="10">
@@ -16462,34 +16389,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00257</v>
+        <v>0.0026</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00172</v>
+        <v>0.00175</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00379</v>
+        <v>0.0038</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00277</v>
+        <v>0.00279</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00393</v>
+        <v>0.00386</v>
       </c>
       <c r="G10" t="n">
         <v>0.00178</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00967</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00319</v>
+        <v>0.0032</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01799</v>
+        <v>0.01786</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00381</v>
+        <v>0.00378</v>
       </c>
     </row>
     <row r="11">
@@ -16499,34 +16426,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.00263</v>
+        <v>0.00264</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00229</v>
+        <v>0.00231</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00311</v>
+        <v>0.00312</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0032</v>
+        <v>0.00322</v>
       </c>
       <c r="F11" t="n">
         <v>0.00474</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00284</v>
+        <v>0.00285</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00615</v>
+        <v>0.00616</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00501</v>
+        <v>0.00504</v>
       </c>
       <c r="J11" t="n">
-        <v>0.00381</v>
+        <v>0.00378</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0089</v>
+        <v>0.00893</v>
       </c>
     </row>
   </sheetData>
@@ -16602,7 +16529,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01388</v>
+        <v>0.01392</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -16642,7 +16569,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01388</v>
+        <v>0.01392</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -16682,7 +16609,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01388</v>
+        <v>0.01392</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16722,7 +16649,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01388</v>
+        <v>0.01392</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -16762,7 +16689,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01388</v>
+        <v>0.01392</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -16802,7 +16729,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01388</v>
+        <v>0.01392</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -16842,7 +16769,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01388</v>
+        <v>0.01392</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -16882,7 +16809,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01388</v>
+        <v>0.01392</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -16922,7 +16849,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01388</v>
+        <v>0.01392</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -16962,7 +16889,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01388</v>
+        <v>0.01392</v>
       </c>
     </row>
   </sheetData>
@@ -17038,34 +16965,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00662</v>
+        <v>0.00666</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00216</v>
+        <v>0.00217</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0019</v>
+        <v>0.00192</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00276</v>
+        <v>0.00278</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00404</v>
+        <v>0.00406</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00187</v>
+        <v>0.00189</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00382</v>
+        <v>0.00384</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00483</v>
+        <v>0.00486</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00231</v>
+        <v>0.00234</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00236</v>
+        <v>0.00238</v>
       </c>
     </row>
     <row r="3">
@@ -17075,34 +17002,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00216</v>
+        <v>0.00217</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00521</v>
+        <v>0.00524</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00197</v>
+        <v>0.00198</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00278</v>
+        <v>0.0028</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00379</v>
+        <v>0.00382</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00183</v>
+        <v>0.00184</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00381</v>
+        <v>0.00384</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00303</v>
+        <v>0.00305</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00155</v>
+        <v>0.00157</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00206</v>
+        <v>0.00208</v>
       </c>
     </row>
     <row r="4">
@@ -17112,34 +17039,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0019</v>
+        <v>0.00192</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00197</v>
+        <v>0.00198</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00614</v>
+        <v>0.00617</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0035</v>
+        <v>0.00352</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00317</v>
+        <v>0.00319</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00231</v>
+        <v>0.00232</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00449</v>
+        <v>0.00451</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0033</v>
+        <v>0.00332</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00341</v>
+        <v>0.00342</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0028</v>
+        <v>0.00281</v>
       </c>
     </row>
     <row r="5">
@@ -17149,34 +17076,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00276</v>
+        <v>0.00278</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00278</v>
+        <v>0.0028</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0035</v>
+        <v>0.00352</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00808</v>
+        <v>0.00812</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00475</v>
+        <v>0.00478</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00324</v>
+        <v>0.00326</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00638</v>
+        <v>0.00641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00458</v>
+        <v>0.0046</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0025</v>
+        <v>0.00251</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00288</v>
+        <v>0.0029</v>
       </c>
     </row>
     <row r="6">
@@ -17186,34 +17113,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00404</v>
+        <v>0.00406</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00379</v>
+        <v>0.00382</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00317</v>
+        <v>0.00319</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00475</v>
+        <v>0.00478</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01438</v>
+        <v>0.01443</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00397</v>
+        <v>0.00398</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00958</v>
+        <v>0.00959</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00588</v>
+        <v>0.00591</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00354</v>
+        <v>0.00348</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00426</v>
+        <v>0.00427</v>
       </c>
     </row>
     <row r="7">
@@ -17223,34 +17150,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00187</v>
+        <v>0.00189</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00183</v>
+        <v>0.00184</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00231</v>
+        <v>0.00232</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00324</v>
+        <v>0.00326</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00397</v>
+        <v>0.00398</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01206</v>
+        <v>0.01213</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00452</v>
+        <v>0.00454</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00466</v>
+        <v>0.00469</v>
       </c>
       <c r="J7" t="n">
         <v>0.0016</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00255</v>
+        <v>0.00257</v>
       </c>
     </row>
     <row r="8">
@@ -17260,31 +17187,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00382</v>
+        <v>0.00384</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00381</v>
+        <v>0.00384</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00449</v>
+        <v>0.00451</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00638</v>
+        <v>0.00641</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00958</v>
+        <v>0.00959</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00452</v>
+        <v>0.00454</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0288</v>
+        <v>0.02889</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00708</v>
+        <v>0.00711</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.00864</v>
       </c>
       <c r="K8" t="n">
         <v>0.00554</v>
@@ -17297,34 +17224,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00483</v>
+        <v>0.00486</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00303</v>
+        <v>0.00305</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0033</v>
+        <v>0.00332</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00458</v>
+        <v>0.0046</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00588</v>
+        <v>0.00591</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00466</v>
+        <v>0.00469</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00708</v>
+        <v>0.00711</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03054</v>
+        <v>0.03071</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00287</v>
+        <v>0.00288</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00451</v>
+        <v>0.00453</v>
       </c>
     </row>
     <row r="10">
@@ -17334,34 +17261,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00231</v>
+        <v>0.00234</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00155</v>
+        <v>0.00157</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00341</v>
+        <v>0.00342</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0025</v>
+        <v>0.00251</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00354</v>
+        <v>0.00348</v>
       </c>
       <c r="G10" t="n">
         <v>0.0016</v>
       </c>
       <c r="H10" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.00864</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00287</v>
+        <v>0.00288</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01758</v>
+        <v>0.01746</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00343</v>
+        <v>0.0034</v>
       </c>
     </row>
     <row r="11">
@@ -17371,34 +17298,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.00236</v>
+        <v>0.00238</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00206</v>
+        <v>0.00208</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0028</v>
+        <v>0.00281</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00288</v>
+        <v>0.0029</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00426</v>
+        <v>0.00427</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00255</v>
+        <v>0.00257</v>
       </c>
       <c r="H11" t="n">
         <v>0.00554</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00451</v>
+        <v>0.00453</v>
       </c>
       <c r="J11" t="n">
-        <v>0.00343</v>
+        <v>0.0034</v>
       </c>
       <c r="K11" t="n">
-        <v>0.009390000000000001</v>
+        <v>0.009429999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -17474,7 +17401,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00581</v>
+        <v>0.00585</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -17514,7 +17441,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00425</v>
+        <v>0.00427</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -17554,7 +17481,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00528</v>
+        <v>0.00531</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -17594,7 +17521,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00743</v>
+        <v>0.00748</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -17634,7 +17561,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01444</v>
+        <v>0.01449</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -17674,7 +17601,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01186</v>
+        <v>0.01193</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -17714,7 +17641,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03045</v>
+        <v>0.03056</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -17754,7 +17681,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03239</v>
+        <v>0.03258</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -17794,7 +17721,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01799</v>
+        <v>0.01786</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -17834,7 +17761,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0089</v>
+        <v>0.00893</v>
       </c>
     </row>
   </sheetData>
@@ -17910,34 +17837,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00581</v>
+        <v>0.00585</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00218</v>
+        <v>0.00219</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00192</v>
+        <v>0.00193</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00279</v>
+        <v>0.0028</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00407</v>
+        <v>0.0041</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00189</v>
+        <v>0.0019</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00385</v>
+        <v>0.00388</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00488</v>
+        <v>0.0049</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00234</v>
+        <v>0.00236</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00239</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="3">
@@ -17947,34 +17874,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00218</v>
+        <v>0.00219</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00425</v>
+        <v>0.00427</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00199</v>
+        <v>0.002</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00281</v>
+        <v>0.00282</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00382</v>
+        <v>0.00385</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00185</v>
+        <v>0.00186</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00384</v>
+        <v>0.00387</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00306</v>
+        <v>0.00308</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00156</v>
+        <v>0.00159</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00208</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="4">
@@ -17984,34 +17911,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00192</v>
+        <v>0.00193</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00199</v>
+        <v>0.002</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00528</v>
+        <v>0.00531</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00353</v>
+        <v>0.00355</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0032</v>
+        <v>0.00322</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00233</v>
+        <v>0.00234</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00453</v>
+        <v>0.00455</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00333</v>
+        <v>0.00335</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00344</v>
+        <v>0.00345</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00282</v>
+        <v>0.00283</v>
       </c>
     </row>
     <row r="5">
@@ -18021,34 +17948,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00279</v>
+        <v>0.0028</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00281</v>
+        <v>0.00282</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00353</v>
+        <v>0.00355</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00743</v>
+        <v>0.00748</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00479</v>
+        <v>0.00482</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00327</v>
+        <v>0.00329</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00643</v>
+        <v>0.00647</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00462</v>
+        <v>0.00464</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00252</v>
+        <v>0.00253</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00291</v>
+        <v>0.00292</v>
       </c>
     </row>
     <row r="6">
@@ -18058,34 +17985,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00407</v>
+        <v>0.0041</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00382</v>
+        <v>0.00385</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0032</v>
+        <v>0.00322</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00479</v>
+        <v>0.00482</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01444</v>
+        <v>0.01449</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004</v>
+        <v>0.00402</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00967</v>
+        <v>0.009679999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00593</v>
+        <v>0.00596</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00357</v>
+        <v>0.00351</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0043</v>
+        <v>0.00431</v>
       </c>
     </row>
     <row r="7">
@@ -18095,34 +18022,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00189</v>
+        <v>0.0019</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00185</v>
+        <v>0.00186</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00233</v>
+        <v>0.00234</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00327</v>
+        <v>0.00329</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004</v>
+        <v>0.00402</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01186</v>
+        <v>0.01193</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00456</v>
+        <v>0.00458</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00471</v>
+        <v>0.00473</v>
       </c>
       <c r="J7" t="n">
         <v>0.00162</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00258</v>
+        <v>0.00259</v>
       </c>
     </row>
     <row r="8">
@@ -18132,31 +18059,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00385</v>
+        <v>0.00388</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00384</v>
+        <v>0.00387</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00453</v>
+        <v>0.00455</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00643</v>
+        <v>0.00647</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00967</v>
+        <v>0.009679999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00456</v>
+        <v>0.00458</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03045</v>
+        <v>0.03056</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00714</v>
+        <v>0.00718</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00878</v>
+        <v>0.00872</v>
       </c>
       <c r="K8" t="n">
         <v>0.00559</v>
@@ -18169,34 +18096,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00488</v>
+        <v>0.0049</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00306</v>
+        <v>0.00308</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00333</v>
+        <v>0.00335</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00462</v>
+        <v>0.00464</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00593</v>
+        <v>0.00596</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00471</v>
+        <v>0.00473</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00714</v>
+        <v>0.00718</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03239</v>
+        <v>0.03258</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0029</v>
+        <v>0.00291</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00455</v>
+        <v>0.00457</v>
       </c>
     </row>
     <row r="10">
@@ -18206,34 +18133,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00234</v>
+        <v>0.00236</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00156</v>
+        <v>0.00159</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00344</v>
+        <v>0.00345</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00252</v>
+        <v>0.00253</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00357</v>
+        <v>0.00351</v>
       </c>
       <c r="G10" t="n">
         <v>0.00162</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00878</v>
+        <v>0.00872</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0029</v>
+        <v>0.00291</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01799</v>
+        <v>0.01786</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00346</v>
+        <v>0.00343</v>
       </c>
     </row>
     <row r="11">
@@ -18243,34 +18170,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.00239</v>
+        <v>0.0024</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00208</v>
+        <v>0.0021</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00282</v>
+        <v>0.00283</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00291</v>
+        <v>0.00292</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0043</v>
+        <v>0.00431</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00258</v>
+        <v>0.00259</v>
       </c>
       <c r="H11" t="n">
         <v>0.00559</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00455</v>
+        <v>0.00457</v>
       </c>
       <c r="J11" t="n">
-        <v>0.00346</v>
+        <v>0.00343</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0089</v>
+        <v>0.00893</v>
       </c>
     </row>
   </sheetData>
@@ -18349,31 +18276,31 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.48218</v>
+        <v>0.48211</v>
       </c>
       <c r="D2" t="n">
-        <v>0.38191</v>
+        <v>0.38206</v>
       </c>
       <c r="E2" t="n">
-        <v>0.46684</v>
+        <v>0.46688</v>
       </c>
       <c r="F2" t="n">
-        <v>0.48926</v>
+        <v>0.49034</v>
       </c>
       <c r="G2" t="n">
-        <v>0.25081</v>
+        <v>0.25087</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31854</v>
+        <v>0.31936</v>
       </c>
       <c r="I2" t="n">
-        <v>0.39108</v>
+        <v>0.39114</v>
       </c>
       <c r="J2" t="n">
-        <v>0.25134</v>
+        <v>0.25411</v>
       </c>
       <c r="K2" t="n">
-        <v>0.36509</v>
+        <v>0.36574</v>
       </c>
     </row>
     <row r="3">
@@ -18383,34 +18310,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.48218</v>
+        <v>0.48211</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.46172</v>
+        <v>0.46214</v>
       </c>
       <c r="E3" t="n">
-        <v>0.55006</v>
+        <v>0.55026</v>
       </c>
       <c r="F3" t="n">
-        <v>0.53695</v>
+        <v>0.5389</v>
       </c>
       <c r="G3" t="n">
-        <v>0.28658</v>
+        <v>0.28679</v>
       </c>
       <c r="H3" t="n">
-        <v>0.37172</v>
+        <v>0.37335</v>
       </c>
       <c r="I3" t="n">
-        <v>0.28726</v>
+        <v>0.28744</v>
       </c>
       <c r="J3" t="n">
-        <v>0.19631</v>
+        <v>0.20037</v>
       </c>
       <c r="K3" t="n">
-        <v>0.37263</v>
+        <v>0.37392</v>
       </c>
     </row>
     <row r="4">
@@ -18420,34 +18347,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.38191</v>
+        <v>0.38206</v>
       </c>
       <c r="C4" t="n">
-        <v>0.46172</v>
+        <v>0.46214</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.62047</v>
+        <v>0.62049</v>
       </c>
       <c r="F4" t="n">
-        <v>0.40381</v>
+        <v>0.40376</v>
       </c>
       <c r="G4" t="n">
-        <v>0.32422</v>
+        <v>0.32419</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3934</v>
+        <v>0.39333</v>
       </c>
       <c r="I4" t="n">
-        <v>0.28071</v>
+        <v>0.28068</v>
       </c>
       <c r="J4" t="n">
-        <v>0.38864</v>
+        <v>0.38993</v>
       </c>
       <c r="K4" t="n">
-        <v>0.45328</v>
+        <v>0.45321</v>
       </c>
     </row>
     <row r="5">
@@ -18457,34 +18384,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.46684</v>
+        <v>0.46688</v>
       </c>
       <c r="C5" t="n">
-        <v>0.55006</v>
+        <v>0.55026</v>
       </c>
       <c r="D5" t="n">
-        <v>0.62047</v>
+        <v>0.62049</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.50927</v>
+        <v>0.50979</v>
       </c>
       <c r="G5" t="n">
-        <v>0.38364</v>
+        <v>0.38363</v>
       </c>
       <c r="H5" t="n">
-        <v>0.47075</v>
+        <v>0.47117</v>
       </c>
       <c r="I5" t="n">
-        <v>0.32766</v>
+        <v>0.32765</v>
       </c>
       <c r="J5" t="n">
-        <v>0.23981</v>
+        <v>0.24116</v>
       </c>
       <c r="K5" t="n">
-        <v>0.39367</v>
+        <v>0.39388</v>
       </c>
     </row>
     <row r="6">
@@ -18494,34 +18421,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.48926</v>
+        <v>0.49034</v>
       </c>
       <c r="C6" t="n">
-        <v>0.53695</v>
+        <v>0.5389</v>
       </c>
       <c r="D6" t="n">
-        <v>0.40381</v>
+        <v>0.40376</v>
       </c>
       <c r="E6" t="n">
-        <v>0.50927</v>
+        <v>0.50979</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.33668</v>
+        <v>0.33683</v>
       </c>
       <c r="H6" t="n">
-        <v>0.50774</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.30202</v>
+        <v>0.30218</v>
       </c>
       <c r="J6" t="n">
-        <v>0.24385</v>
+        <v>0.24011</v>
       </c>
       <c r="K6" t="n">
-        <v>0.41799</v>
+        <v>0.41692</v>
       </c>
     </row>
     <row r="7">
@@ -18531,34 +18458,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25081</v>
+        <v>0.25087</v>
       </c>
       <c r="C7" t="n">
-        <v>0.28658</v>
+        <v>0.28679</v>
       </c>
       <c r="D7" t="n">
-        <v>0.32422</v>
+        <v>0.32419</v>
       </c>
       <c r="E7" t="n">
-        <v>0.38364</v>
+        <v>0.38363</v>
       </c>
       <c r="F7" t="n">
-        <v>0.33668</v>
+        <v>0.33683</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.26442</v>
+        <v>0.26446</v>
       </c>
       <c r="I7" t="n">
-        <v>0.26429</v>
+        <v>0.26427</v>
       </c>
       <c r="J7" t="n">
-        <v>0.12177</v>
+        <v>0.12196</v>
       </c>
       <c r="K7" t="n">
-        <v>0.27627</v>
+        <v>0.27628</v>
       </c>
     </row>
     <row r="8">
@@ -18568,34 +18495,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.31854</v>
+        <v>0.31936</v>
       </c>
       <c r="C8" t="n">
-        <v>0.37172</v>
+        <v>0.37335</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3934</v>
+        <v>0.39333</v>
       </c>
       <c r="E8" t="n">
-        <v>0.47075</v>
+        <v>0.47117</v>
       </c>
       <c r="F8" t="n">
-        <v>0.50774</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>0.26442</v>
+        <v>0.26446</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.25037</v>
+        <v>0.25045</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41317</v>
+        <v>0.41093</v>
       </c>
       <c r="K8" t="n">
-        <v>0.37397</v>
+        <v>0.37285</v>
       </c>
     </row>
     <row r="9">
@@ -18605,34 +18532,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.39108</v>
+        <v>0.39114</v>
       </c>
       <c r="C9" t="n">
-        <v>0.28726</v>
+        <v>0.28744</v>
       </c>
       <c r="D9" t="n">
-        <v>0.28071</v>
+        <v>0.28068</v>
       </c>
       <c r="E9" t="n">
-        <v>0.32766</v>
+        <v>0.32765</v>
       </c>
       <c r="F9" t="n">
-        <v>0.30202</v>
+        <v>0.30218</v>
       </c>
       <c r="G9" t="n">
-        <v>0.26429</v>
+        <v>0.26427</v>
       </c>
       <c r="H9" t="n">
-        <v>0.25037</v>
+        <v>0.25045</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1323</v>
+        <v>0.13268</v>
       </c>
       <c r="K9" t="n">
-        <v>0.29522</v>
+        <v>0.29527</v>
       </c>
     </row>
     <row r="10">
@@ -18642,34 +18569,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.25134</v>
+        <v>0.25411</v>
       </c>
       <c r="C10" t="n">
-        <v>0.19631</v>
+        <v>0.20037</v>
       </c>
       <c r="D10" t="n">
-        <v>0.38864</v>
+        <v>0.38993</v>
       </c>
       <c r="E10" t="n">
-        <v>0.23981</v>
+        <v>0.24116</v>
       </c>
       <c r="F10" t="n">
-        <v>0.24385</v>
+        <v>0.24011</v>
       </c>
       <c r="G10" t="n">
-        <v>0.12177</v>
+        <v>0.12196</v>
       </c>
       <c r="H10" t="n">
-        <v>0.41317</v>
+        <v>0.41093</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1323</v>
+        <v>0.13268</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.30148</v>
+        <v>0.29928</v>
       </c>
     </row>
     <row r="11">
@@ -18679,31 +18606,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.36509</v>
+        <v>0.36574</v>
       </c>
       <c r="C11" t="n">
-        <v>0.37263</v>
+        <v>0.37392</v>
       </c>
       <c r="D11" t="n">
-        <v>0.45328</v>
+        <v>0.45321</v>
       </c>
       <c r="E11" t="n">
-        <v>0.39367</v>
+        <v>0.39388</v>
       </c>
       <c r="F11" t="n">
-        <v>0.41799</v>
+        <v>0.41692</v>
       </c>
       <c r="G11" t="n">
-        <v>0.27627</v>
+        <v>0.27628</v>
       </c>
       <c r="H11" t="n">
-        <v>0.37397</v>
+        <v>0.37285</v>
       </c>
       <c r="I11" t="n">
-        <v>0.29522</v>
+        <v>0.29527</v>
       </c>
       <c r="J11" t="n">
-        <v>0.30148</v>
+        <v>0.29928</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
